--- a/0-course-info/canvas/canvas_schedule.xlsx
+++ b/0-course-info/canvas/canvas_schedule.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10830"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10909"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/czmann/Documents/teaching/stat3540/0-course-info/canvas/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE412575-6D37-D24A-9F3C-55B7BFA30C15}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20A29B55-40CF-914B-AD77-6C3786F30758}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="17740" yWindow="-18800" windowWidth="27240" windowHeight="16180" xr2:uid="{BA0A3FFF-9577-8249-B793-6919848B638A}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17880" xr2:uid="{BA0A3FFF-9577-8249-B793-6919848B638A}"/>
   </bookViews>
   <sheets>
     <sheet name="schedule" sheetId="2" r:id="rId1"/>
@@ -134,9 +134,6 @@
     <t>Lecture Video: 3-way factorial</t>
   </si>
   <si>
-    <t>Activity 4.3</t>
-  </si>
-  <si>
     <t>Mod 5: RCBD</t>
   </si>
   <si>
@@ -258,6 +255,9 @@
   </si>
   <si>
     <t>Lab 2 data collection due 9/20</t>
+  </si>
+  <si>
+    <t>Lab 2 work time</t>
   </si>
 </sst>
 </file>
@@ -507,11 +507,20 @@
     <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -524,15 +533,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -906,7 +906,7 @@
       </c>
     </row>
     <row r="2" spans="1:8" ht="32" x14ac:dyDescent="0.2">
-      <c r="A2" s="47">
+      <c r="A2" s="49">
         <v>1</v>
       </c>
       <c r="B2" s="4">
@@ -929,7 +929,7 @@
       </c>
     </row>
     <row r="3" spans="1:8" ht="32" x14ac:dyDescent="0.2">
-      <c r="A3" s="47"/>
+      <c r="A3" s="49"/>
       <c r="B3" s="4">
         <v>2</v>
       </c>
@@ -944,14 +944,14 @@
         <v>8</v>
       </c>
       <c r="F3" s="9" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G3" s="9" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="20.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="48"/>
+      <c r="A4" s="50"/>
       <c r="B4" s="10"/>
       <c r="C4" s="10"/>
       <c r="D4" s="11"/>
@@ -959,11 +959,11 @@
       <c r="F4" s="13"/>
       <c r="G4" s="13"/>
       <c r="H4" s="14" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="48" x14ac:dyDescent="0.2">
-      <c r="A5" s="53">
+      <c r="A5" s="48">
         <v>2</v>
       </c>
       <c r="B5" s="15">
@@ -989,7 +989,7 @@
       <c r="H5" s="19"/>
     </row>
     <row r="6" spans="1:8" ht="48" x14ac:dyDescent="0.2">
-      <c r="A6" s="47"/>
+      <c r="A6" s="49"/>
       <c r="B6" s="4">
         <f>B5+1</f>
         <v>4</v>
@@ -1012,7 +1012,7 @@
       </c>
     </row>
     <row r="7" spans="1:8" ht="20.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="48"/>
+      <c r="A7" s="50"/>
       <c r="B7" s="10"/>
       <c r="C7" s="10"/>
       <c r="D7" s="11"/>
@@ -1022,7 +1022,7 @@
       <c r="H7" s="14"/>
     </row>
     <row r="8" spans="1:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="A8" s="47">
+      <c r="A8" s="49">
         <v>3</v>
       </c>
       <c r="B8" s="4">
@@ -1046,11 +1046,11 @@
         <v>20</v>
       </c>
       <c r="H8" s="8" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="20.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="47"/>
+      <c r="A9" s="49"/>
       <c r="B9" s="4">
         <f>B8+1</f>
         <v>6</v>
@@ -1073,7 +1073,7 @@
       </c>
     </row>
     <row r="10" spans="1:8" ht="20.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="48"/>
+      <c r="A10" s="50"/>
       <c r="B10" s="10"/>
       <c r="C10" s="10"/>
       <c r="D10" s="11"/>
@@ -1081,11 +1081,11 @@
       <c r="F10" s="13"/>
       <c r="G10" s="13"/>
       <c r="H10" s="14" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="32" x14ac:dyDescent="0.2">
-      <c r="A11" s="53">
+      <c r="A11" s="48">
         <v>4</v>
       </c>
       <c r="B11" s="15">
@@ -1110,7 +1110,7 @@
       </c>
     </row>
     <row r="12" spans="1:8" ht="20.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="47"/>
+      <c r="A12" s="49"/>
       <c r="B12" s="21">
         <f>B11+1</f>
         <v>8</v>
@@ -1125,14 +1125,14 @@
       <c r="E12" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="F12" s="55" t="s">
+      <c r="F12" s="47" t="s">
         <v>27</v>
       </c>
-      <c r="G12" s="55"/>
-      <c r="H12" s="55"/>
+      <c r="G12" s="47"/>
+      <c r="H12" s="47"/>
     </row>
     <row r="13" spans="1:8" ht="20.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="48"/>
+      <c r="A13" s="50"/>
       <c r="B13" s="10"/>
       <c r="C13" s="10"/>
       <c r="D13" s="11"/>
@@ -1140,11 +1140,11 @@
       <c r="F13" s="13"/>
       <c r="G13" s="13"/>
       <c r="H13" s="31" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="20.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="53">
+      <c r="A14" s="48">
         <v>5</v>
       </c>
       <c r="B14" s="15">
@@ -1165,12 +1165,12 @@
         <v>28</v>
       </c>
       <c r="G14" s="9" t="s">
-        <v>29</v>
+        <v>68</v>
       </c>
       <c r="H14" s="19"/>
     </row>
     <row r="15" spans="1:8" ht="48" x14ac:dyDescent="0.2">
-      <c r="A15" s="47"/>
+      <c r="A15" s="49"/>
       <c r="B15" s="4">
         <f>B14+1</f>
         <v>10</v>
@@ -1183,18 +1183,18 @@
         <v>46289</v>
       </c>
       <c r="E15" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="F15" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="F15" s="9" t="s">
+      <c r="G15" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="G15" s="9" t="s">
-        <v>32</v>
-      </c>
       <c r="H15" s="24"/>
     </row>
     <row r="16" spans="1:8" ht="20.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="48"/>
+      <c r="A16" s="50"/>
       <c r="B16" s="10"/>
       <c r="C16" s="10"/>
       <c r="D16" s="11"/>
@@ -1202,11 +1202,11 @@
       <c r="F16" s="13"/>
       <c r="G16" s="13"/>
       <c r="H16" s="14" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="17" spans="1:9" ht="16" x14ac:dyDescent="0.2">
-      <c r="A17" s="53">
+      <c r="A17" s="48">
         <v>6</v>
       </c>
       <c r="B17" s="15">
@@ -1221,17 +1221,17 @@
         <v>46294</v>
       </c>
       <c r="E17" s="6" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F17" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="G17" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="G17" s="9" t="s">
-        <v>35</v>
-      </c>
     </row>
     <row r="18" spans="1:9" ht="32" x14ac:dyDescent="0.2">
-      <c r="A18" s="47"/>
+      <c r="A18" s="49"/>
       <c r="B18" s="4">
         <f>B17+1</f>
         <v>12</v>
@@ -1244,17 +1244,17 @@
         <v>46296</v>
       </c>
       <c r="E18" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="F18" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="F18" s="9" t="s">
+      <c r="G18" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="G18" s="9" t="s">
-        <v>38</v>
-      </c>
     </row>
     <row r="19" spans="1:9" ht="20.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="48"/>
+      <c r="A19" s="50"/>
       <c r="B19" s="10"/>
       <c r="C19" s="10"/>
       <c r="D19" s="11"/>
@@ -1263,7 +1263,7 @@
       <c r="H19" s="25"/>
     </row>
     <row r="20" spans="1:9" ht="20.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="53">
+      <c r="A20" s="48">
         <v>7</v>
       </c>
       <c r="B20" s="15">
@@ -1278,18 +1278,18 @@
         <v>46301</v>
       </c>
       <c r="E20" s="17" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F20" t="s">
+        <v>38</v>
+      </c>
+      <c r="G20" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="G20" s="9" t="s">
-        <v>40</v>
-      </c>
       <c r="H20" s="18"/>
     </row>
     <row r="21" spans="1:9" ht="48" x14ac:dyDescent="0.2">
-      <c r="A21" s="47"/>
+      <c r="A21" s="49"/>
       <c r="B21" s="4">
         <f>B20+1</f>
         <v>14</v>
@@ -1302,28 +1302,28 @@
         <v>46303</v>
       </c>
       <c r="E21" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="F21" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="F21" s="9" t="s">
+      <c r="G21" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="G21" s="9" t="s">
-        <v>43</v>
-      </c>
     </row>
     <row r="22" spans="1:9" ht="20.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="48"/>
+      <c r="A22" s="50"/>
       <c r="B22" s="10"/>
       <c r="C22" s="10"/>
       <c r="D22" s="11"/>
-      <c r="F22" s="54" t="s">
-        <v>44</v>
-      </c>
-      <c r="G22" s="54"/>
-      <c r="H22" s="54"/>
+      <c r="F22" s="51" t="s">
+        <v>43</v>
+      </c>
+      <c r="G22" s="51"/>
+      <c r="H22" s="51"/>
     </row>
     <row r="23" spans="1:9" ht="20.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="53">
+      <c r="A23" s="48">
         <v>8</v>
       </c>
       <c r="B23" s="15">
@@ -1338,7 +1338,7 @@
         <v>46308</v>
       </c>
       <c r="E23" s="17" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F23" s="18"/>
       <c r="G23" s="18"/>
@@ -1346,7 +1346,7 @@
       <c r="I23" s="8"/>
     </row>
     <row r="24" spans="1:9" ht="20.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="47"/>
+      <c r="A24" s="49"/>
       <c r="B24" s="4">
         <f>B23+1</f>
         <v>16</v>
@@ -1359,23 +1359,23 @@
         <v>46310</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="H24" s="26"/>
     </row>
     <row r="25" spans="1:9" ht="20.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="48"/>
+      <c r="A25" s="50"/>
       <c r="B25" s="10"/>
       <c r="C25" s="10"/>
       <c r="D25" s="11"/>
       <c r="F25" s="13"/>
       <c r="G25" s="13"/>
       <c r="H25" s="14" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="26" spans="1:9" ht="20.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="53">
+      <c r="A26" s="48">
         <v>9</v>
       </c>
       <c r="B26" s="27">
@@ -1390,14 +1390,14 @@
         <v>46315</v>
       </c>
       <c r="E26" s="29" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F26" s="30"/>
       <c r="G26" s="30"/>
       <c r="H26" s="30"/>
     </row>
     <row r="27" spans="1:9" ht="20.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="47"/>
+      <c r="A27" s="49"/>
       <c r="B27" s="4">
         <f>B26+1</f>
         <v>18</v>
@@ -1410,15 +1410,15 @@
         <v>46317</v>
       </c>
       <c r="E27" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="G27" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="G27" s="9" t="s">
-        <v>49</v>
-      </c>
       <c r="H27" s="31"/>
     </row>
     <row r="28" spans="1:9" ht="20.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="48"/>
+      <c r="A28" s="50"/>
       <c r="B28" s="10"/>
       <c r="C28" s="10"/>
       <c r="D28" s="11"/>
@@ -1428,7 +1428,7 @@
       <c r="H28" s="14"/>
     </row>
     <row r="29" spans="1:9" ht="20.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="47">
+      <c r="A29" s="49">
         <v>10</v>
       </c>
       <c r="B29" s="15">
@@ -1443,12 +1443,12 @@
         <v>46322</v>
       </c>
       <c r="E29" s="6" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="H29" s="9"/>
     </row>
     <row r="30" spans="1:9" ht="20.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="47"/>
+      <c r="A30" s="49"/>
       <c r="B30" s="4">
         <f>B29+1</f>
         <v>20</v>
@@ -1461,11 +1461,11 @@
         <v>46324</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="31" spans="1:9" ht="20.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="48"/>
+      <c r="A31" s="50"/>
       <c r="B31" s="10"/>
       <c r="C31" s="10"/>
       <c r="D31" s="11"/>
@@ -1475,7 +1475,7 @@
       <c r="H31" s="34"/>
     </row>
     <row r="32" spans="1:9" ht="16" x14ac:dyDescent="0.2">
-      <c r="A32" s="47">
+      <c r="A32" s="49">
         <v>11</v>
       </c>
       <c r="B32" s="15">
@@ -1490,14 +1490,14 @@
         <v>46329</v>
       </c>
       <c r="E32" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="H32" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="H32" s="9" t="s">
-        <v>51</v>
-      </c>
     </row>
     <row r="33" spans="1:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="A33" s="47"/>
+      <c r="A33" s="49"/>
       <c r="B33" s="4">
         <f>B32+1</f>
         <v>22</v>
@@ -1510,11 +1510,11 @@
         <v>46331</v>
       </c>
       <c r="E33" s="6" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A34" s="48"/>
+      <c r="A34" s="50"/>
       <c r="B34" s="10"/>
       <c r="C34" s="10"/>
       <c r="D34" s="11"/>
@@ -1524,7 +1524,7 @@
       <c r="H34" s="34"/>
     </row>
     <row r="35" spans="1:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="A35" s="47">
+      <c r="A35" s="49">
         <v>12</v>
       </c>
       <c r="B35" s="15">
@@ -1539,12 +1539,12 @@
         <v>46336</v>
       </c>
       <c r="E35" s="6" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="H35" s="9"/>
     </row>
     <row r="36" spans="1:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="A36" s="47"/>
+      <c r="A36" s="49"/>
       <c r="B36" s="4">
         <f>B35+1</f>
         <v>24</v>
@@ -1557,11 +1557,11 @@
         <v>46338</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A37" s="48"/>
+      <c r="A37" s="50"/>
       <c r="B37" s="10"/>
       <c r="C37" s="10"/>
       <c r="D37" s="11"/>
@@ -1571,7 +1571,7 @@
       <c r="H37" s="34"/>
     </row>
     <row r="38" spans="1:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="A38" s="47">
+      <c r="A38" s="49">
         <v>13</v>
       </c>
       <c r="B38" s="15">
@@ -1586,12 +1586,12 @@
         <v>46343</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="H38" s="9"/>
     </row>
     <row r="39" spans="1:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="A39" s="47"/>
+      <c r="A39" s="49"/>
       <c r="B39" s="4">
         <f>B38+1</f>
         <v>26</v>
@@ -1604,11 +1604,11 @@
         <v>46345</v>
       </c>
       <c r="E39" s="6" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A40" s="48"/>
+      <c r="A40" s="50"/>
       <c r="B40" s="10"/>
       <c r="C40" s="10"/>
       <c r="D40" s="11"/>
@@ -1616,11 +1616,11 @@
       <c r="F40" s="33"/>
       <c r="G40" s="33"/>
       <c r="H40" s="25" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A41" s="51"/>
+      <c r="A41" s="54"/>
       <c r="B41" s="36"/>
       <c r="C41" s="35" t="s">
         <v>7</v>
@@ -1635,7 +1635,7 @@
       <c r="H41" s="39"/>
     </row>
     <row r="42" spans="1:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="A42" s="51"/>
+      <c r="A42" s="54"/>
       <c r="B42" s="35"/>
       <c r="C42" s="35" t="s">
         <v>11</v>
@@ -1645,14 +1645,14 @@
         <v>46352</v>
       </c>
       <c r="E42" s="38" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F42" s="39"/>
       <c r="G42" s="39"/>
       <c r="H42" s="41"/>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A43" s="52"/>
+      <c r="A43" s="55"/>
       <c r="B43" s="42"/>
       <c r="C43" s="42"/>
       <c r="D43" s="43"/>
@@ -1662,7 +1662,7 @@
       <c r="H43" s="46"/>
     </row>
     <row r="44" spans="1:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="A44" s="47">
+      <c r="A44" s="49">
         <v>14</v>
       </c>
       <c r="B44" s="15">
@@ -1677,12 +1677,12 @@
         <v>46357</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="H44" s="9"/>
     </row>
     <row r="45" spans="1:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="A45" s="47"/>
+      <c r="A45" s="49"/>
       <c r="B45" s="4">
         <f>B44+1</f>
         <v>28</v>
@@ -1695,11 +1695,11 @@
         <v>46359</v>
       </c>
       <c r="E45" s="6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A46" s="48"/>
+      <c r="A46" s="50"/>
       <c r="B46" s="10"/>
       <c r="C46" s="10"/>
       <c r="D46" s="11">
@@ -1712,7 +1712,7 @@
       <c r="H46" s="34"/>
     </row>
     <row r="47" spans="1:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="A47" s="47">
+      <c r="A47" s="49">
         <v>15</v>
       </c>
       <c r="B47" s="15">
@@ -1727,14 +1727,14 @@
         <v>46364</v>
       </c>
       <c r="E47" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="H47" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="H47" s="8" t="s">
-        <v>56</v>
-      </c>
     </row>
     <row r="48" spans="1:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="A48" s="47"/>
+      <c r="A48" s="49"/>
       <c r="B48" s="4">
         <f>B47+1</f>
         <v>30</v>
@@ -1747,14 +1747,14 @@
         <v>46366</v>
       </c>
       <c r="E48" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="H48" s="8" t="s">
         <v>57</v>
       </c>
-      <c r="H48" s="8" t="s">
-        <v>58</v>
-      </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A49" s="48"/>
+      <c r="A49" s="50"/>
       <c r="B49" s="10"/>
       <c r="C49" s="10"/>
       <c r="D49" s="11">
@@ -1767,7 +1767,7 @@
       <c r="H49" s="34"/>
     </row>
     <row r="50" spans="1:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="A50" s="47"/>
+      <c r="A50" s="49"/>
       <c r="B50" s="15"/>
       <c r="C50" s="4" t="s">
         <v>7</v>
@@ -1777,14 +1777,14 @@
         <v>46371</v>
       </c>
       <c r="E50" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="H50" s="52" t="s">
         <v>59</v>
       </c>
-      <c r="H50" s="49" t="s">
-        <v>60</v>
-      </c>
     </row>
     <row r="51" spans="1:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="A51" s="47"/>
+      <c r="A51" s="49"/>
       <c r="C51" s="4" t="s">
         <v>11</v>
       </c>
@@ -1793,17 +1793,17 @@
         <v>46373</v>
       </c>
       <c r="E51" s="6" t="s">
-        <v>61</v>
-      </c>
-      <c r="H51" s="50"/>
+        <v>60</v>
+      </c>
+      <c r="H51" s="53"/>
     </row>
     <row r="52" spans="1:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="A52" s="48"/>
+      <c r="A52" s="50"/>
       <c r="B52" s="10"/>
       <c r="C52" s="10"/>
       <c r="D52" s="11"/>
       <c r="E52" s="12" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="F52" s="33"/>
       <c r="G52" s="33"/>
@@ -1811,6 +1811,14 @@
     </row>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="A50:A52"/>
+    <mergeCell ref="H50:H51"/>
+    <mergeCell ref="A32:A34"/>
+    <mergeCell ref="A35:A37"/>
+    <mergeCell ref="A38:A40"/>
+    <mergeCell ref="A41:A43"/>
+    <mergeCell ref="A44:A46"/>
+    <mergeCell ref="A47:A49"/>
     <mergeCell ref="F12:H12"/>
     <mergeCell ref="A14:A16"/>
     <mergeCell ref="A29:A31"/>
@@ -1823,14 +1831,6 @@
     <mergeCell ref="F22:H22"/>
     <mergeCell ref="A23:A25"/>
     <mergeCell ref="A26:A28"/>
-    <mergeCell ref="A50:A52"/>
-    <mergeCell ref="H50:H51"/>
-    <mergeCell ref="A32:A34"/>
-    <mergeCell ref="A35:A37"/>
-    <mergeCell ref="A38:A40"/>
-    <mergeCell ref="A41:A43"/>
-    <mergeCell ref="A44:A46"/>
-    <mergeCell ref="A47:A49"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup scale="78" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>

--- a/0-course-info/canvas/canvas_schedule.xlsx
+++ b/0-course-info/canvas/canvas_schedule.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/czmann/Documents/teaching/stat3540/0-course-info/canvas/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20A29B55-40CF-914B-AD77-6C3786F30758}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2BE5F913-EED1-9B46-B401-B808834996E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17880" xr2:uid="{BA0A3FFF-9577-8249-B793-6919848B638A}"/>
   </bookViews>
@@ -145,13 +145,7 @@
     <t>Activity 5.1</t>
   </si>
   <si>
-    <t>Lab 2 due 9/25</t>
-  </si>
-  <si>
     <t>Lecture Video: RCBD + Factorials</t>
-  </si>
-  <si>
-    <t>Activity 5.2</t>
   </si>
   <si>
     <t>Mod 6: Random / Fixed Effects Models</t>
@@ -159,9 +153,6 @@
   <si>
     <t>Lecture Video: Random vs Fixed Effects
 Lecture Video: Mixed Model (Blocks)</t>
-  </si>
-  <si>
-    <t>Activity 6.1 + Start Lab 3</t>
   </si>
   <si>
     <t>Lecture Video: Subsampling (random effects)</t>
@@ -258,6 +249,15 @@
   </si>
   <si>
     <t>Lab 2 work time</t>
+  </si>
+  <si>
+    <t>Lab 2 due 9/29</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Activity 6.1 </t>
+  </si>
+  <si>
+    <t>Activity 5.2 + Start Lab 3</t>
   </si>
 </sst>
 </file>
@@ -507,32 +507,32 @@
     <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -906,7 +906,7 @@
       </c>
     </row>
     <row r="2" spans="1:8" ht="32" x14ac:dyDescent="0.2">
-      <c r="A2" s="49">
+      <c r="A2" s="47">
         <v>1</v>
       </c>
       <c r="B2" s="4">
@@ -929,7 +929,7 @@
       </c>
     </row>
     <row r="3" spans="1:8" ht="32" x14ac:dyDescent="0.2">
-      <c r="A3" s="49"/>
+      <c r="A3" s="47"/>
       <c r="B3" s="4">
         <v>2</v>
       </c>
@@ -944,14 +944,14 @@
         <v>8</v>
       </c>
       <c r="F3" s="9" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="G3" s="9" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="20.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="50"/>
+      <c r="A4" s="48"/>
       <c r="B4" s="10"/>
       <c r="C4" s="10"/>
       <c r="D4" s="11"/>
@@ -959,11 +959,11 @@
       <c r="F4" s="13"/>
       <c r="G4" s="13"/>
       <c r="H4" s="14" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="48" x14ac:dyDescent="0.2">
-      <c r="A5" s="48">
+      <c r="A5" s="54">
         <v>2</v>
       </c>
       <c r="B5" s="15">
@@ -989,7 +989,7 @@
       <c r="H5" s="19"/>
     </row>
     <row r="6" spans="1:8" ht="48" x14ac:dyDescent="0.2">
-      <c r="A6" s="49"/>
+      <c r="A6" s="47"/>
       <c r="B6" s="4">
         <f>B5+1</f>
         <v>4</v>
@@ -1012,7 +1012,7 @@
       </c>
     </row>
     <row r="7" spans="1:8" ht="20.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="50"/>
+      <c r="A7" s="48"/>
       <c r="B7" s="10"/>
       <c r="C7" s="10"/>
       <c r="D7" s="11"/>
@@ -1022,7 +1022,7 @@
       <c r="H7" s="14"/>
     </row>
     <row r="8" spans="1:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="A8" s="49">
+      <c r="A8" s="47">
         <v>3</v>
       </c>
       <c r="B8" s="4">
@@ -1046,11 +1046,11 @@
         <v>20</v>
       </c>
       <c r="H8" s="8" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="20.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="49"/>
+      <c r="A9" s="47"/>
       <c r="B9" s="4">
         <f>B8+1</f>
         <v>6</v>
@@ -1073,7 +1073,7 @@
       </c>
     </row>
     <row r="10" spans="1:8" ht="20.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="50"/>
+      <c r="A10" s="48"/>
       <c r="B10" s="10"/>
       <c r="C10" s="10"/>
       <c r="D10" s="11"/>
@@ -1081,11 +1081,11 @@
       <c r="F10" s="13"/>
       <c r="G10" s="13"/>
       <c r="H10" s="14" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="32" x14ac:dyDescent="0.2">
-      <c r="A11" s="48">
+      <c r="A11" s="54">
         <v>4</v>
       </c>
       <c r="B11" s="15">
@@ -1110,7 +1110,7 @@
       </c>
     </row>
     <row r="12" spans="1:8" ht="20.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="49"/>
+      <c r="A12" s="47"/>
       <c r="B12" s="21">
         <f>B11+1</f>
         <v>8</v>
@@ -1125,14 +1125,14 @@
       <c r="E12" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="F12" s="47" t="s">
+      <c r="F12" s="53" t="s">
         <v>27</v>
       </c>
-      <c r="G12" s="47"/>
-      <c r="H12" s="47"/>
+      <c r="G12" s="53"/>
+      <c r="H12" s="53"/>
     </row>
     <row r="13" spans="1:8" ht="20.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="50"/>
+      <c r="A13" s="48"/>
       <c r="B13" s="10"/>
       <c r="C13" s="10"/>
       <c r="D13" s="11"/>
@@ -1140,11 +1140,11 @@
       <c r="F13" s="13"/>
       <c r="G13" s="13"/>
       <c r="H13" s="31" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="20.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="48">
+      <c r="A14" s="54">
         <v>5</v>
       </c>
       <c r="B14" s="15">
@@ -1165,12 +1165,12 @@
         <v>28</v>
       </c>
       <c r="G14" s="9" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="H14" s="19"/>
     </row>
     <row r="15" spans="1:8" ht="48" x14ac:dyDescent="0.2">
-      <c r="A15" s="49"/>
+      <c r="A15" s="47"/>
       <c r="B15" s="4">
         <f>B14+1</f>
         <v>10</v>
@@ -1194,19 +1194,17 @@
       <c r="H15" s="24"/>
     </row>
     <row r="16" spans="1:8" ht="20.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="50"/>
+      <c r="A16" s="48"/>
       <c r="B16" s="10"/>
       <c r="C16" s="10"/>
       <c r="D16" s="11"/>
       <c r="E16" s="12"/>
       <c r="F16" s="13"/>
       <c r="G16" s="13"/>
-      <c r="H16" s="14" t="s">
-        <v>32</v>
-      </c>
+      <c r="H16" s="14"/>
     </row>
     <row r="17" spans="1:9" ht="16" x14ac:dyDescent="0.2">
-      <c r="A17" s="48">
+      <c r="A17" s="54">
         <v>6</v>
       </c>
       <c r="B17" s="15">
@@ -1224,14 +1222,17 @@
         <v>29</v>
       </c>
       <c r="F17" s="9" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G17" s="9" t="s">
-        <v>34</v>
+        <v>68</v>
+      </c>
+      <c r="H17" s="14" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="18" spans="1:9" ht="32" x14ac:dyDescent="0.2">
-      <c r="A18" s="49"/>
+      <c r="A18" s="47"/>
       <c r="B18" s="4">
         <f>B17+1</f>
         <v>12</v>
@@ -1244,17 +1245,17 @@
         <v>46296</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="F18" s="9" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="G18" s="9" t="s">
-        <v>37</v>
+        <v>67</v>
       </c>
     </row>
     <row r="19" spans="1:9" ht="20.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="50"/>
+      <c r="A19" s="48"/>
       <c r="B19" s="10"/>
       <c r="C19" s="10"/>
       <c r="D19" s="11"/>
@@ -1263,7 +1264,7 @@
       <c r="H19" s="25"/>
     </row>
     <row r="20" spans="1:9" ht="20.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="48">
+      <c r="A20" s="54">
         <v>7</v>
       </c>
       <c r="B20" s="15">
@@ -1278,18 +1279,18 @@
         <v>46301</v>
       </c>
       <c r="E20" s="17" t="s">
+        <v>33</v>
+      </c>
+      <c r="F20" t="s">
         <v>35</v>
       </c>
-      <c r="F20" t="s">
-        <v>38</v>
-      </c>
       <c r="G20" s="9" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="H20" s="18"/>
     </row>
     <row r="21" spans="1:9" ht="48" x14ac:dyDescent="0.2">
-      <c r="A21" s="49"/>
+      <c r="A21" s="47"/>
       <c r="B21" s="4">
         <f>B20+1</f>
         <v>14</v>
@@ -1302,28 +1303,28 @@
         <v>46303</v>
       </c>
       <c r="E21" s="6" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="F21" s="9" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="G21" s="9" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
     </row>
     <row r="22" spans="1:9" ht="20.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="50"/>
+      <c r="A22" s="48"/>
       <c r="B22" s="10"/>
       <c r="C22" s="10"/>
       <c r="D22" s="11"/>
-      <c r="F22" s="51" t="s">
-        <v>43</v>
-      </c>
-      <c r="G22" s="51"/>
-      <c r="H22" s="51"/>
+      <c r="F22" s="55" t="s">
+        <v>40</v>
+      </c>
+      <c r="G22" s="55"/>
+      <c r="H22" s="55"/>
     </row>
     <row r="23" spans="1:9" ht="20.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="48">
+      <c r="A23" s="54">
         <v>8</v>
       </c>
       <c r="B23" s="15">
@@ -1338,7 +1339,7 @@
         <v>46308</v>
       </c>
       <c r="E23" s="17" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="F23" s="18"/>
       <c r="G23" s="18"/>
@@ -1346,7 +1347,7 @@
       <c r="I23" s="8"/>
     </row>
     <row r="24" spans="1:9" ht="20.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="49"/>
+      <c r="A24" s="47"/>
       <c r="B24" s="4">
         <f>B23+1</f>
         <v>16</v>
@@ -1359,23 +1360,23 @@
         <v>46310</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="H24" s="26"/>
     </row>
     <row r="25" spans="1:9" ht="20.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="50"/>
+      <c r="A25" s="48"/>
       <c r="B25" s="10"/>
       <c r="C25" s="10"/>
       <c r="D25" s="11"/>
       <c r="F25" s="13"/>
       <c r="G25" s="13"/>
       <c r="H25" s="14" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
     </row>
     <row r="26" spans="1:9" ht="20.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="48">
+      <c r="A26" s="54">
         <v>9</v>
       </c>
       <c r="B26" s="27">
@@ -1390,14 +1391,14 @@
         <v>46315</v>
       </c>
       <c r="E26" s="29" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="F26" s="30"/>
       <c r="G26" s="30"/>
       <c r="H26" s="30"/>
     </row>
     <row r="27" spans="1:9" ht="20.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="49"/>
+      <c r="A27" s="47"/>
       <c r="B27" s="4">
         <f>B26+1</f>
         <v>18</v>
@@ -1410,15 +1411,15 @@
         <v>46317</v>
       </c>
       <c r="E27" s="6" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="G27" s="9" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="H27" s="31"/>
     </row>
     <row r="28" spans="1:9" ht="20.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="50"/>
+      <c r="A28" s="48"/>
       <c r="B28" s="10"/>
       <c r="C28" s="10"/>
       <c r="D28" s="11"/>
@@ -1428,7 +1429,7 @@
       <c r="H28" s="14"/>
     </row>
     <row r="29" spans="1:9" ht="20.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="49">
+      <c r="A29" s="47">
         <v>10</v>
       </c>
       <c r="B29" s="15">
@@ -1443,12 +1444,12 @@
         <v>46322</v>
       </c>
       <c r="E29" s="6" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="H29" s="9"/>
     </row>
     <row r="30" spans="1:9" ht="20.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="49"/>
+      <c r="A30" s="47"/>
       <c r="B30" s="4">
         <f>B29+1</f>
         <v>20</v>
@@ -1461,11 +1462,11 @@
         <v>46324</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
     </row>
     <row r="31" spans="1:9" ht="20.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="50"/>
+      <c r="A31" s="48"/>
       <c r="B31" s="10"/>
       <c r="C31" s="10"/>
       <c r="D31" s="11"/>
@@ -1475,7 +1476,7 @@
       <c r="H31" s="34"/>
     </row>
     <row r="32" spans="1:9" ht="16" x14ac:dyDescent="0.2">
-      <c r="A32" s="49">
+      <c r="A32" s="47">
         <v>11</v>
       </c>
       <c r="B32" s="15">
@@ -1490,14 +1491,14 @@
         <v>46329</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="H32" s="9" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
     </row>
     <row r="33" spans="1:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="A33" s="49"/>
+      <c r="A33" s="47"/>
       <c r="B33" s="4">
         <f>B32+1</f>
         <v>22</v>
@@ -1510,11 +1511,11 @@
         <v>46331</v>
       </c>
       <c r="E33" s="6" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A34" s="50"/>
+      <c r="A34" s="48"/>
       <c r="B34" s="10"/>
       <c r="C34" s="10"/>
       <c r="D34" s="11"/>
@@ -1524,7 +1525,7 @@
       <c r="H34" s="34"/>
     </row>
     <row r="35" spans="1:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="A35" s="49">
+      <c r="A35" s="47">
         <v>12</v>
       </c>
       <c r="B35" s="15">
@@ -1539,12 +1540,12 @@
         <v>46336</v>
       </c>
       <c r="E35" s="6" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="H35" s="9"/>
     </row>
     <row r="36" spans="1:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="A36" s="49"/>
+      <c r="A36" s="47"/>
       <c r="B36" s="4">
         <f>B35+1</f>
         <v>24</v>
@@ -1557,11 +1558,11 @@
         <v>46338</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A37" s="50"/>
+      <c r="A37" s="48"/>
       <c r="B37" s="10"/>
       <c r="C37" s="10"/>
       <c r="D37" s="11"/>
@@ -1571,7 +1572,7 @@
       <c r="H37" s="34"/>
     </row>
     <row r="38" spans="1:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="A38" s="49">
+      <c r="A38" s="47">
         <v>13</v>
       </c>
       <c r="B38" s="15">
@@ -1586,12 +1587,12 @@
         <v>46343</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="H38" s="9"/>
     </row>
     <row r="39" spans="1:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="A39" s="49"/>
+      <c r="A39" s="47"/>
       <c r="B39" s="4">
         <f>B38+1</f>
         <v>26</v>
@@ -1604,11 +1605,11 @@
         <v>46345</v>
       </c>
       <c r="E39" s="6" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A40" s="50"/>
+      <c r="A40" s="48"/>
       <c r="B40" s="10"/>
       <c r="C40" s="10"/>
       <c r="D40" s="11"/>
@@ -1616,11 +1617,11 @@
       <c r="F40" s="33"/>
       <c r="G40" s="33"/>
       <c r="H40" s="25" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A41" s="54"/>
+      <c r="A41" s="51"/>
       <c r="B41" s="36"/>
       <c r="C41" s="35" t="s">
         <v>7</v>
@@ -1635,7 +1636,7 @@
       <c r="H41" s="39"/>
     </row>
     <row r="42" spans="1:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="A42" s="54"/>
+      <c r="A42" s="51"/>
       <c r="B42" s="35"/>
       <c r="C42" s="35" t="s">
         <v>11</v>
@@ -1645,14 +1646,14 @@
         <v>46352</v>
       </c>
       <c r="E42" s="38" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="F42" s="39"/>
       <c r="G42" s="39"/>
       <c r="H42" s="41"/>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A43" s="55"/>
+      <c r="A43" s="52"/>
       <c r="B43" s="42"/>
       <c r="C43" s="42"/>
       <c r="D43" s="43"/>
@@ -1662,7 +1663,7 @@
       <c r="H43" s="46"/>
     </row>
     <row r="44" spans="1:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="A44" s="49">
+      <c r="A44" s="47">
         <v>14</v>
       </c>
       <c r="B44" s="15">
@@ -1677,12 +1678,12 @@
         <v>46357</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="H44" s="9"/>
     </row>
     <row r="45" spans="1:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="A45" s="49"/>
+      <c r="A45" s="47"/>
       <c r="B45" s="4">
         <f>B44+1</f>
         <v>28</v>
@@ -1695,11 +1696,11 @@
         <v>46359</v>
       </c>
       <c r="E45" s="6" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A46" s="50"/>
+      <c r="A46" s="48"/>
       <c r="B46" s="10"/>
       <c r="C46" s="10"/>
       <c r="D46" s="11">
@@ -1712,7 +1713,7 @@
       <c r="H46" s="34"/>
     </row>
     <row r="47" spans="1:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="A47" s="49">
+      <c r="A47" s="47">
         <v>15</v>
       </c>
       <c r="B47" s="15">
@@ -1727,14 +1728,14 @@
         <v>46364</v>
       </c>
       <c r="E47" s="6" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="H47" s="8" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
     </row>
     <row r="48" spans="1:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="A48" s="49"/>
+      <c r="A48" s="47"/>
       <c r="B48" s="4">
         <f>B47+1</f>
         <v>30</v>
@@ -1747,14 +1748,14 @@
         <v>46366</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="H48" s="8" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A49" s="50"/>
+      <c r="A49" s="48"/>
       <c r="B49" s="10"/>
       <c r="C49" s="10"/>
       <c r="D49" s="11">
@@ -1767,7 +1768,7 @@
       <c r="H49" s="34"/>
     </row>
     <row r="50" spans="1:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="A50" s="49"/>
+      <c r="A50" s="47"/>
       <c r="B50" s="15"/>
       <c r="C50" s="4" t="s">
         <v>7</v>
@@ -1777,14 +1778,14 @@
         <v>46371</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="H50" s="52" t="s">
-        <v>59</v>
+        <v>55</v>
+      </c>
+      <c r="H50" s="49" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="51" spans="1:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="A51" s="49"/>
+      <c r="A51" s="47"/>
       <c r="C51" s="4" t="s">
         <v>11</v>
       </c>
@@ -1793,17 +1794,17 @@
         <v>46373</v>
       </c>
       <c r="E51" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="H51" s="53"/>
+        <v>57</v>
+      </c>
+      <c r="H51" s="50"/>
     </row>
     <row r="52" spans="1:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="A52" s="50"/>
+      <c r="A52" s="48"/>
       <c r="B52" s="10"/>
       <c r="C52" s="10"/>
       <c r="D52" s="11"/>
       <c r="E52" s="12" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="F52" s="33"/>
       <c r="G52" s="33"/>
@@ -1811,14 +1812,6 @@
     </row>
   </sheetData>
   <mergeCells count="20">
-    <mergeCell ref="A50:A52"/>
-    <mergeCell ref="H50:H51"/>
-    <mergeCell ref="A32:A34"/>
-    <mergeCell ref="A35:A37"/>
-    <mergeCell ref="A38:A40"/>
-    <mergeCell ref="A41:A43"/>
-    <mergeCell ref="A44:A46"/>
-    <mergeCell ref="A47:A49"/>
     <mergeCell ref="F12:H12"/>
     <mergeCell ref="A14:A16"/>
     <mergeCell ref="A29:A31"/>
@@ -1831,6 +1824,14 @@
     <mergeCell ref="F22:H22"/>
     <mergeCell ref="A23:A25"/>
     <mergeCell ref="A26:A28"/>
+    <mergeCell ref="A50:A52"/>
+    <mergeCell ref="H50:H51"/>
+    <mergeCell ref="A32:A34"/>
+    <mergeCell ref="A35:A37"/>
+    <mergeCell ref="A38:A40"/>
+    <mergeCell ref="A41:A43"/>
+    <mergeCell ref="A44:A46"/>
+    <mergeCell ref="A47:A49"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup scale="78" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>

--- a/0-course-info/canvas/canvas_schedule.xlsx
+++ b/0-course-info/canvas/canvas_schedule.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/czmann/Documents/teaching/stat3540/0-course-info/canvas/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2BE5F913-EED1-9B46-B401-B808834996E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03EB46EB-E43B-294C-B013-E24CA7F32BE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17880" xr2:uid="{BA0A3FFF-9577-8249-B793-6919848B638A}"/>
   </bookViews>
@@ -507,11 +507,20 @@
     <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -524,15 +533,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -906,7 +906,7 @@
       </c>
     </row>
     <row r="2" spans="1:8" ht="32" x14ac:dyDescent="0.2">
-      <c r="A2" s="47">
+      <c r="A2" s="49">
         <v>1</v>
       </c>
       <c r="B2" s="4">
@@ -929,7 +929,7 @@
       </c>
     </row>
     <row r="3" spans="1:8" ht="32" x14ac:dyDescent="0.2">
-      <c r="A3" s="47"/>
+      <c r="A3" s="49"/>
       <c r="B3" s="4">
         <v>2</v>
       </c>
@@ -951,7 +951,7 @@
       </c>
     </row>
     <row r="4" spans="1:8" ht="20.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="48"/>
+      <c r="A4" s="50"/>
       <c r="B4" s="10"/>
       <c r="C4" s="10"/>
       <c r="D4" s="11"/>
@@ -963,7 +963,7 @@
       </c>
     </row>
     <row r="5" spans="1:8" ht="48" x14ac:dyDescent="0.2">
-      <c r="A5" s="54">
+      <c r="A5" s="48">
         <v>2</v>
       </c>
       <c r="B5" s="15">
@@ -989,7 +989,7 @@
       <c r="H5" s="19"/>
     </row>
     <row r="6" spans="1:8" ht="48" x14ac:dyDescent="0.2">
-      <c r="A6" s="47"/>
+      <c r="A6" s="49"/>
       <c r="B6" s="4">
         <f>B5+1</f>
         <v>4</v>
@@ -1012,7 +1012,7 @@
       </c>
     </row>
     <row r="7" spans="1:8" ht="20.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="48"/>
+      <c r="A7" s="50"/>
       <c r="B7" s="10"/>
       <c r="C7" s="10"/>
       <c r="D7" s="11"/>
@@ -1022,7 +1022,7 @@
       <c r="H7" s="14"/>
     </row>
     <row r="8" spans="1:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="A8" s="47">
+      <c r="A8" s="49">
         <v>3</v>
       </c>
       <c r="B8" s="4">
@@ -1050,7 +1050,7 @@
       </c>
     </row>
     <row r="9" spans="1:8" ht="20.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="47"/>
+      <c r="A9" s="49"/>
       <c r="B9" s="4">
         <f>B8+1</f>
         <v>6</v>
@@ -1073,7 +1073,7 @@
       </c>
     </row>
     <row r="10" spans="1:8" ht="20.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="48"/>
+      <c r="A10" s="50"/>
       <c r="B10" s="10"/>
       <c r="C10" s="10"/>
       <c r="D10" s="11"/>
@@ -1085,7 +1085,7 @@
       </c>
     </row>
     <row r="11" spans="1:8" ht="32" x14ac:dyDescent="0.2">
-      <c r="A11" s="54">
+      <c r="A11" s="48">
         <v>4</v>
       </c>
       <c r="B11" s="15">
@@ -1110,7 +1110,7 @@
       </c>
     </row>
     <row r="12" spans="1:8" ht="20.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="47"/>
+      <c r="A12" s="49"/>
       <c r="B12" s="21">
         <f>B11+1</f>
         <v>8</v>
@@ -1125,14 +1125,14 @@
       <c r="E12" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="F12" s="53" t="s">
+      <c r="F12" s="47" t="s">
         <v>27</v>
       </c>
-      <c r="G12" s="53"/>
-      <c r="H12" s="53"/>
+      <c r="G12" s="47"/>
+      <c r="H12" s="47"/>
     </row>
     <row r="13" spans="1:8" ht="20.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="48"/>
+      <c r="A13" s="50"/>
       <c r="B13" s="10"/>
       <c r="C13" s="10"/>
       <c r="D13" s="11"/>
@@ -1144,7 +1144,7 @@
       </c>
     </row>
     <row r="14" spans="1:8" ht="20.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="54">
+      <c r="A14" s="48">
         <v>5</v>
       </c>
       <c r="B14" s="15">
@@ -1170,7 +1170,7 @@
       <c r="H14" s="19"/>
     </row>
     <row r="15" spans="1:8" ht="48" x14ac:dyDescent="0.2">
-      <c r="A15" s="47"/>
+      <c r="A15" s="49"/>
       <c r="B15" s="4">
         <f>B14+1</f>
         <v>10</v>
@@ -1194,7 +1194,7 @@
       <c r="H15" s="24"/>
     </row>
     <row r="16" spans="1:8" ht="20.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="48"/>
+      <c r="A16" s="50"/>
       <c r="B16" s="10"/>
       <c r="C16" s="10"/>
       <c r="D16" s="11"/>
@@ -1204,7 +1204,7 @@
       <c r="H16" s="14"/>
     </row>
     <row r="17" spans="1:9" ht="16" x14ac:dyDescent="0.2">
-      <c r="A17" s="54">
+      <c r="A17" s="48">
         <v>6</v>
       </c>
       <c r="B17" s="15">
@@ -1227,12 +1227,12 @@
       <c r="G17" s="9" t="s">
         <v>68</v>
       </c>
-      <c r="H17" s="14" t="s">
+      <c r="H17" s="9" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="18" spans="1:9" ht="32" x14ac:dyDescent="0.2">
-      <c r="A18" s="47"/>
+      <c r="A18" s="49"/>
       <c r="B18" s="4">
         <f>B17+1</f>
         <v>12</v>
@@ -1255,7 +1255,7 @@
       </c>
     </row>
     <row r="19" spans="1:9" ht="20.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="48"/>
+      <c r="A19" s="50"/>
       <c r="B19" s="10"/>
       <c r="C19" s="10"/>
       <c r="D19" s="11"/>
@@ -1264,7 +1264,7 @@
       <c r="H19" s="25"/>
     </row>
     <row r="20" spans="1:9" ht="20.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="54">
+      <c r="A20" s="48">
         <v>7</v>
       </c>
       <c r="B20" s="15">
@@ -1290,7 +1290,7 @@
       <c r="H20" s="18"/>
     </row>
     <row r="21" spans="1:9" ht="48" x14ac:dyDescent="0.2">
-      <c r="A21" s="47"/>
+      <c r="A21" s="49"/>
       <c r="B21" s="4">
         <f>B20+1</f>
         <v>14</v>
@@ -1313,18 +1313,18 @@
       </c>
     </row>
     <row r="22" spans="1:9" ht="20.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="48"/>
+      <c r="A22" s="50"/>
       <c r="B22" s="10"/>
       <c r="C22" s="10"/>
       <c r="D22" s="11"/>
-      <c r="F22" s="55" t="s">
+      <c r="F22" s="51" t="s">
         <v>40</v>
       </c>
-      <c r="G22" s="55"/>
-      <c r="H22" s="55"/>
+      <c r="G22" s="51"/>
+      <c r="H22" s="51"/>
     </row>
     <row r="23" spans="1:9" ht="20.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="54">
+      <c r="A23" s="48">
         <v>8</v>
       </c>
       <c r="B23" s="15">
@@ -1347,7 +1347,7 @@
       <c r="I23" s="8"/>
     </row>
     <row r="24" spans="1:9" ht="20.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="47"/>
+      <c r="A24" s="49"/>
       <c r="B24" s="4">
         <f>B23+1</f>
         <v>16</v>
@@ -1365,7 +1365,7 @@
       <c r="H24" s="26"/>
     </row>
     <row r="25" spans="1:9" ht="20.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="48"/>
+      <c r="A25" s="50"/>
       <c r="B25" s="10"/>
       <c r="C25" s="10"/>
       <c r="D25" s="11"/>
@@ -1376,7 +1376,7 @@
       </c>
     </row>
     <row r="26" spans="1:9" ht="20.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="54">
+      <c r="A26" s="48">
         <v>9</v>
       </c>
       <c r="B26" s="27">
@@ -1398,7 +1398,7 @@
       <c r="H26" s="30"/>
     </row>
     <row r="27" spans="1:9" ht="20.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="47"/>
+      <c r="A27" s="49"/>
       <c r="B27" s="4">
         <f>B26+1</f>
         <v>18</v>
@@ -1419,7 +1419,7 @@
       <c r="H27" s="31"/>
     </row>
     <row r="28" spans="1:9" ht="20.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="48"/>
+      <c r="A28" s="50"/>
       <c r="B28" s="10"/>
       <c r="C28" s="10"/>
       <c r="D28" s="11"/>
@@ -1429,7 +1429,7 @@
       <c r="H28" s="14"/>
     </row>
     <row r="29" spans="1:9" ht="20.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="47">
+      <c r="A29" s="49">
         <v>10</v>
       </c>
       <c r="B29" s="15">
@@ -1449,7 +1449,7 @@
       <c r="H29" s="9"/>
     </row>
     <row r="30" spans="1:9" ht="20.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="47"/>
+      <c r="A30" s="49"/>
       <c r="B30" s="4">
         <f>B29+1</f>
         <v>20</v>
@@ -1466,7 +1466,7 @@
       </c>
     </row>
     <row r="31" spans="1:9" ht="20.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="48"/>
+      <c r="A31" s="50"/>
       <c r="B31" s="10"/>
       <c r="C31" s="10"/>
       <c r="D31" s="11"/>
@@ -1476,7 +1476,7 @@
       <c r="H31" s="34"/>
     </row>
     <row r="32" spans="1:9" ht="16" x14ac:dyDescent="0.2">
-      <c r="A32" s="47">
+      <c r="A32" s="49">
         <v>11</v>
       </c>
       <c r="B32" s="15">
@@ -1498,7 +1498,7 @@
       </c>
     </row>
     <row r="33" spans="1:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="A33" s="47"/>
+      <c r="A33" s="49"/>
       <c r="B33" s="4">
         <f>B32+1</f>
         <v>22</v>
@@ -1515,7 +1515,7 @@
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A34" s="48"/>
+      <c r="A34" s="50"/>
       <c r="B34" s="10"/>
       <c r="C34" s="10"/>
       <c r="D34" s="11"/>
@@ -1525,7 +1525,7 @@
       <c r="H34" s="34"/>
     </row>
     <row r="35" spans="1:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="A35" s="47">
+      <c r="A35" s="49">
         <v>12</v>
       </c>
       <c r="B35" s="15">
@@ -1545,7 +1545,7 @@
       <c r="H35" s="9"/>
     </row>
     <row r="36" spans="1:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="A36" s="47"/>
+      <c r="A36" s="49"/>
       <c r="B36" s="4">
         <f>B35+1</f>
         <v>24</v>
@@ -1562,7 +1562,7 @@
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A37" s="48"/>
+      <c r="A37" s="50"/>
       <c r="B37" s="10"/>
       <c r="C37" s="10"/>
       <c r="D37" s="11"/>
@@ -1572,7 +1572,7 @@
       <c r="H37" s="34"/>
     </row>
     <row r="38" spans="1:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="A38" s="47">
+      <c r="A38" s="49">
         <v>13</v>
       </c>
       <c r="B38" s="15">
@@ -1592,7 +1592,7 @@
       <c r="H38" s="9"/>
     </row>
     <row r="39" spans="1:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="A39" s="47"/>
+      <c r="A39" s="49"/>
       <c r="B39" s="4">
         <f>B38+1</f>
         <v>26</v>
@@ -1609,7 +1609,7 @@
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A40" s="48"/>
+      <c r="A40" s="50"/>
       <c r="B40" s="10"/>
       <c r="C40" s="10"/>
       <c r="D40" s="11"/>
@@ -1621,7 +1621,7 @@
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A41" s="51"/>
+      <c r="A41" s="54"/>
       <c r="B41" s="36"/>
       <c r="C41" s="35" t="s">
         <v>7</v>
@@ -1636,7 +1636,7 @@
       <c r="H41" s="39"/>
     </row>
     <row r="42" spans="1:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="A42" s="51"/>
+      <c r="A42" s="54"/>
       <c r="B42" s="35"/>
       <c r="C42" s="35" t="s">
         <v>11</v>
@@ -1653,7 +1653,7 @@
       <c r="H42" s="41"/>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A43" s="52"/>
+      <c r="A43" s="55"/>
       <c r="B43" s="42"/>
       <c r="C43" s="42"/>
       <c r="D43" s="43"/>
@@ -1663,7 +1663,7 @@
       <c r="H43" s="46"/>
     </row>
     <row r="44" spans="1:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="A44" s="47">
+      <c r="A44" s="49">
         <v>14</v>
       </c>
       <c r="B44" s="15">
@@ -1683,7 +1683,7 @@
       <c r="H44" s="9"/>
     </row>
     <row r="45" spans="1:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="A45" s="47"/>
+      <c r="A45" s="49"/>
       <c r="B45" s="4">
         <f>B44+1</f>
         <v>28</v>
@@ -1700,7 +1700,7 @@
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A46" s="48"/>
+      <c r="A46" s="50"/>
       <c r="B46" s="10"/>
       <c r="C46" s="10"/>
       <c r="D46" s="11">
@@ -1713,7 +1713,7 @@
       <c r="H46" s="34"/>
     </row>
     <row r="47" spans="1:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="A47" s="47">
+      <c r="A47" s="49">
         <v>15</v>
       </c>
       <c r="B47" s="15">
@@ -1735,7 +1735,7 @@
       </c>
     </row>
     <row r="48" spans="1:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="A48" s="47"/>
+      <c r="A48" s="49"/>
       <c r="B48" s="4">
         <f>B47+1</f>
         <v>30</v>
@@ -1755,7 +1755,7 @@
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A49" s="48"/>
+      <c r="A49" s="50"/>
       <c r="B49" s="10"/>
       <c r="C49" s="10"/>
       <c r="D49" s="11">
@@ -1768,7 +1768,7 @@
       <c r="H49" s="34"/>
     </row>
     <row r="50" spans="1:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="A50" s="47"/>
+      <c r="A50" s="49"/>
       <c r="B50" s="15"/>
       <c r="C50" s="4" t="s">
         <v>7</v>
@@ -1780,12 +1780,12 @@
       <c r="E50" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="H50" s="49" t="s">
+      <c r="H50" s="52" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="51" spans="1:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="A51" s="47"/>
+      <c r="A51" s="49"/>
       <c r="C51" s="4" t="s">
         <v>11</v>
       </c>
@@ -1796,10 +1796,10 @@
       <c r="E51" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="H51" s="50"/>
+      <c r="H51" s="53"/>
     </row>
     <row r="52" spans="1:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="A52" s="48"/>
+      <c r="A52" s="50"/>
       <c r="B52" s="10"/>
       <c r="C52" s="10"/>
       <c r="D52" s="11"/>
@@ -1812,6 +1812,14 @@
     </row>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="A50:A52"/>
+    <mergeCell ref="H50:H51"/>
+    <mergeCell ref="A32:A34"/>
+    <mergeCell ref="A35:A37"/>
+    <mergeCell ref="A38:A40"/>
+    <mergeCell ref="A41:A43"/>
+    <mergeCell ref="A44:A46"/>
+    <mergeCell ref="A47:A49"/>
     <mergeCell ref="F12:H12"/>
     <mergeCell ref="A14:A16"/>
     <mergeCell ref="A29:A31"/>
@@ -1824,14 +1832,6 @@
     <mergeCell ref="F22:H22"/>
     <mergeCell ref="A23:A25"/>
     <mergeCell ref="A26:A28"/>
-    <mergeCell ref="A50:A52"/>
-    <mergeCell ref="H50:H51"/>
-    <mergeCell ref="A32:A34"/>
-    <mergeCell ref="A35:A37"/>
-    <mergeCell ref="A38:A40"/>
-    <mergeCell ref="A41:A43"/>
-    <mergeCell ref="A44:A46"/>
-    <mergeCell ref="A47:A49"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup scale="78" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>

--- a/0-course-info/canvas/canvas_schedule.xlsx
+++ b/0-course-info/canvas/canvas_schedule.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/czmann/Documents/teaching/stat3540/0-course-info/canvas/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03EB46EB-E43B-294C-B013-E24CA7F32BE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9B91504-18BC-DB4D-AA41-A543C9BC4D3C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17880" xr2:uid="{BA0A3FFF-9577-8249-B793-6919848B638A}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="71">
   <si>
     <t>Week</t>
   </si>
@@ -258,6 +258,12 @@
   </si>
   <si>
     <t>Activity 5.2 + Start Lab 3</t>
+  </si>
+  <si>
+    <t>Lab 3 Optional Checkpoint 1 due 10/2</t>
+  </si>
+  <si>
+    <t>Lab 3 data collection due 10/9</t>
   </si>
 </sst>
 </file>
@@ -507,32 +513,32 @@
     <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -878,7 +884,7 @@
     <col min="5" max="5" width="33.5" style="6" customWidth="1"/>
     <col min="6" max="6" width="35.33203125" style="9" customWidth="1"/>
     <col min="7" max="7" width="21.5" style="9" customWidth="1"/>
-    <col min="8" max="8" width="29" style="8" customWidth="1"/>
+    <col min="8" max="8" width="30.1640625" style="8" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="16" x14ac:dyDescent="0.2">
@@ -906,7 +912,7 @@
       </c>
     </row>
     <row r="2" spans="1:8" ht="32" x14ac:dyDescent="0.2">
-      <c r="A2" s="49">
+      <c r="A2" s="47">
         <v>1</v>
       </c>
       <c r="B2" s="4">
@@ -929,7 +935,7 @@
       </c>
     </row>
     <row r="3" spans="1:8" ht="32" x14ac:dyDescent="0.2">
-      <c r="A3" s="49"/>
+      <c r="A3" s="47"/>
       <c r="B3" s="4">
         <v>2</v>
       </c>
@@ -951,7 +957,7 @@
       </c>
     </row>
     <row r="4" spans="1:8" ht="20.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="50"/>
+      <c r="A4" s="48"/>
       <c r="B4" s="10"/>
       <c r="C4" s="10"/>
       <c r="D4" s="11"/>
@@ -963,7 +969,7 @@
       </c>
     </row>
     <row r="5" spans="1:8" ht="48" x14ac:dyDescent="0.2">
-      <c r="A5" s="48">
+      <c r="A5" s="54">
         <v>2</v>
       </c>
       <c r="B5" s="15">
@@ -989,7 +995,7 @@
       <c r="H5" s="19"/>
     </row>
     <row r="6" spans="1:8" ht="48" x14ac:dyDescent="0.2">
-      <c r="A6" s="49"/>
+      <c r="A6" s="47"/>
       <c r="B6" s="4">
         <f>B5+1</f>
         <v>4</v>
@@ -1012,7 +1018,7 @@
       </c>
     </row>
     <row r="7" spans="1:8" ht="20.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="50"/>
+      <c r="A7" s="48"/>
       <c r="B7" s="10"/>
       <c r="C7" s="10"/>
       <c r="D7" s="11"/>
@@ -1022,7 +1028,7 @@
       <c r="H7" s="14"/>
     </row>
     <row r="8" spans="1:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="A8" s="49">
+      <c r="A8" s="47">
         <v>3</v>
       </c>
       <c r="B8" s="4">
@@ -1050,7 +1056,7 @@
       </c>
     </row>
     <row r="9" spans="1:8" ht="20.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="49"/>
+      <c r="A9" s="47"/>
       <c r="B9" s="4">
         <f>B8+1</f>
         <v>6</v>
@@ -1073,7 +1079,7 @@
       </c>
     </row>
     <row r="10" spans="1:8" ht="20.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="50"/>
+      <c r="A10" s="48"/>
       <c r="B10" s="10"/>
       <c r="C10" s="10"/>
       <c r="D10" s="11"/>
@@ -1085,7 +1091,7 @@
       </c>
     </row>
     <row r="11" spans="1:8" ht="32" x14ac:dyDescent="0.2">
-      <c r="A11" s="48">
+      <c r="A11" s="54">
         <v>4</v>
       </c>
       <c r="B11" s="15">
@@ -1110,7 +1116,7 @@
       </c>
     </row>
     <row r="12" spans="1:8" ht="20.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="49"/>
+      <c r="A12" s="47"/>
       <c r="B12" s="21">
         <f>B11+1</f>
         <v>8</v>
@@ -1125,14 +1131,14 @@
       <c r="E12" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="F12" s="47" t="s">
+      <c r="F12" s="53" t="s">
         <v>27</v>
       </c>
-      <c r="G12" s="47"/>
-      <c r="H12" s="47"/>
+      <c r="G12" s="53"/>
+      <c r="H12" s="53"/>
     </row>
     <row r="13" spans="1:8" ht="20.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="50"/>
+      <c r="A13" s="48"/>
       <c r="B13" s="10"/>
       <c r="C13" s="10"/>
       <c r="D13" s="11"/>
@@ -1144,7 +1150,7 @@
       </c>
     </row>
     <row r="14" spans="1:8" ht="20.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="48">
+      <c r="A14" s="54">
         <v>5</v>
       </c>
       <c r="B14" s="15">
@@ -1170,7 +1176,7 @@
       <c r="H14" s="19"/>
     </row>
     <row r="15" spans="1:8" ht="48" x14ac:dyDescent="0.2">
-      <c r="A15" s="49"/>
+      <c r="A15" s="47"/>
       <c r="B15" s="4">
         <f>B14+1</f>
         <v>10</v>
@@ -1194,7 +1200,7 @@
       <c r="H15" s="24"/>
     </row>
     <row r="16" spans="1:8" ht="20.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="50"/>
+      <c r="A16" s="48"/>
       <c r="B16" s="10"/>
       <c r="C16" s="10"/>
       <c r="D16" s="11"/>
@@ -1204,7 +1210,7 @@
       <c r="H16" s="14"/>
     </row>
     <row r="17" spans="1:9" ht="16" x14ac:dyDescent="0.2">
-      <c r="A17" s="48">
+      <c r="A17" s="54">
         <v>6</v>
       </c>
       <c r="B17" s="15">
@@ -1232,7 +1238,7 @@
       </c>
     </row>
     <row r="18" spans="1:9" ht="32" x14ac:dyDescent="0.2">
-      <c r="A18" s="49"/>
+      <c r="A18" s="47"/>
       <c r="B18" s="4">
         <f>B17+1</f>
         <v>12</v>
@@ -1255,16 +1261,18 @@
       </c>
     </row>
     <row r="19" spans="1:9" ht="20.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="50"/>
+      <c r="A19" s="48"/>
       <c r="B19" s="10"/>
       <c r="C19" s="10"/>
       <c r="D19" s="11"/>
       <c r="F19" s="13"/>
       <c r="G19" s="13"/>
-      <c r="H19" s="25"/>
+      <c r="H19" s="25" t="s">
+        <v>69</v>
+      </c>
     </row>
     <row r="20" spans="1:9" ht="20.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="48">
+      <c r="A20" s="54">
         <v>7</v>
       </c>
       <c r="B20" s="15">
@@ -1290,7 +1298,7 @@
       <c r="H20" s="18"/>
     </row>
     <row r="21" spans="1:9" ht="48" x14ac:dyDescent="0.2">
-      <c r="A21" s="49"/>
+      <c r="A21" s="47"/>
       <c r="B21" s="4">
         <f>B20+1</f>
         <v>14</v>
@@ -1311,20 +1319,23 @@
       <c r="G21" s="9" t="s">
         <v>39</v>
       </c>
+      <c r="H21" s="25" t="s">
+        <v>70</v>
+      </c>
     </row>
     <row r="22" spans="1:9" ht="20.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="50"/>
+      <c r="A22" s="48"/>
       <c r="B22" s="10"/>
       <c r="C22" s="10"/>
       <c r="D22" s="11"/>
-      <c r="F22" s="51" t="s">
+      <c r="F22" s="55" t="s">
         <v>40</v>
       </c>
-      <c r="G22" s="51"/>
-      <c r="H22" s="51"/>
+      <c r="G22" s="55"/>
+      <c r="H22" s="55"/>
     </row>
     <row r="23" spans="1:9" ht="20.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="48">
+      <c r="A23" s="54">
         <v>8</v>
       </c>
       <c r="B23" s="15">
@@ -1347,7 +1358,7 @@
       <c r="I23" s="8"/>
     </row>
     <row r="24" spans="1:9" ht="20.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="49"/>
+      <c r="A24" s="47"/>
       <c r="B24" s="4">
         <f>B23+1</f>
         <v>16</v>
@@ -1365,7 +1376,7 @@
       <c r="H24" s="26"/>
     </row>
     <row r="25" spans="1:9" ht="20.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="50"/>
+      <c r="A25" s="48"/>
       <c r="B25" s="10"/>
       <c r="C25" s="10"/>
       <c r="D25" s="11"/>
@@ -1376,7 +1387,7 @@
       </c>
     </row>
     <row r="26" spans="1:9" ht="20.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="48">
+      <c r="A26" s="54">
         <v>9</v>
       </c>
       <c r="B26" s="27">
@@ -1398,7 +1409,7 @@
       <c r="H26" s="30"/>
     </row>
     <row r="27" spans="1:9" ht="20.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="49"/>
+      <c r="A27" s="47"/>
       <c r="B27" s="4">
         <f>B26+1</f>
         <v>18</v>
@@ -1419,7 +1430,7 @@
       <c r="H27" s="31"/>
     </row>
     <row r="28" spans="1:9" ht="20.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="50"/>
+      <c r="A28" s="48"/>
       <c r="B28" s="10"/>
       <c r="C28" s="10"/>
       <c r="D28" s="11"/>
@@ -1429,7 +1440,7 @@
       <c r="H28" s="14"/>
     </row>
     <row r="29" spans="1:9" ht="20.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="49">
+      <c r="A29" s="47">
         <v>10</v>
       </c>
       <c r="B29" s="15">
@@ -1449,7 +1460,7 @@
       <c r="H29" s="9"/>
     </row>
     <row r="30" spans="1:9" ht="20.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="49"/>
+      <c r="A30" s="47"/>
       <c r="B30" s="4">
         <f>B29+1</f>
         <v>20</v>
@@ -1466,7 +1477,7 @@
       </c>
     </row>
     <row r="31" spans="1:9" ht="20.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="50"/>
+      <c r="A31" s="48"/>
       <c r="B31" s="10"/>
       <c r="C31" s="10"/>
       <c r="D31" s="11"/>
@@ -1476,7 +1487,7 @@
       <c r="H31" s="34"/>
     </row>
     <row r="32" spans="1:9" ht="16" x14ac:dyDescent="0.2">
-      <c r="A32" s="49">
+      <c r="A32" s="47">
         <v>11</v>
       </c>
       <c r="B32" s="15">
@@ -1498,7 +1509,7 @@
       </c>
     </row>
     <row r="33" spans="1:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="A33" s="49"/>
+      <c r="A33" s="47"/>
       <c r="B33" s="4">
         <f>B32+1</f>
         <v>22</v>
@@ -1515,7 +1526,7 @@
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A34" s="50"/>
+      <c r="A34" s="48"/>
       <c r="B34" s="10"/>
       <c r="C34" s="10"/>
       <c r="D34" s="11"/>
@@ -1525,7 +1536,7 @@
       <c r="H34" s="34"/>
     </row>
     <row r="35" spans="1:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="A35" s="49">
+      <c r="A35" s="47">
         <v>12</v>
       </c>
       <c r="B35" s="15">
@@ -1545,7 +1556,7 @@
       <c r="H35" s="9"/>
     </row>
     <row r="36" spans="1:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="A36" s="49"/>
+      <c r="A36" s="47"/>
       <c r="B36" s="4">
         <f>B35+1</f>
         <v>24</v>
@@ -1562,7 +1573,7 @@
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A37" s="50"/>
+      <c r="A37" s="48"/>
       <c r="B37" s="10"/>
       <c r="C37" s="10"/>
       <c r="D37" s="11"/>
@@ -1572,7 +1583,7 @@
       <c r="H37" s="34"/>
     </row>
     <row r="38" spans="1:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="A38" s="49">
+      <c r="A38" s="47">
         <v>13</v>
       </c>
       <c r="B38" s="15">
@@ -1592,7 +1603,7 @@
       <c r="H38" s="9"/>
     </row>
     <row r="39" spans="1:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="A39" s="49"/>
+      <c r="A39" s="47"/>
       <c r="B39" s="4">
         <f>B38+1</f>
         <v>26</v>
@@ -1609,7 +1620,7 @@
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A40" s="50"/>
+      <c r="A40" s="48"/>
       <c r="B40" s="10"/>
       <c r="C40" s="10"/>
       <c r="D40" s="11"/>
@@ -1621,7 +1632,7 @@
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A41" s="54"/>
+      <c r="A41" s="51"/>
       <c r="B41" s="36"/>
       <c r="C41" s="35" t="s">
         <v>7</v>
@@ -1636,7 +1647,7 @@
       <c r="H41" s="39"/>
     </row>
     <row r="42" spans="1:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="A42" s="54"/>
+      <c r="A42" s="51"/>
       <c r="B42" s="35"/>
       <c r="C42" s="35" t="s">
         <v>11</v>
@@ -1653,7 +1664,7 @@
       <c r="H42" s="41"/>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A43" s="55"/>
+      <c r="A43" s="52"/>
       <c r="B43" s="42"/>
       <c r="C43" s="42"/>
       <c r="D43" s="43"/>
@@ -1663,7 +1674,7 @@
       <c r="H43" s="46"/>
     </row>
     <row r="44" spans="1:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="A44" s="49">
+      <c r="A44" s="47">
         <v>14</v>
       </c>
       <c r="B44" s="15">
@@ -1683,7 +1694,7 @@
       <c r="H44" s="9"/>
     </row>
     <row r="45" spans="1:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="A45" s="49"/>
+      <c r="A45" s="47"/>
       <c r="B45" s="4">
         <f>B44+1</f>
         <v>28</v>
@@ -1700,7 +1711,7 @@
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A46" s="50"/>
+      <c r="A46" s="48"/>
       <c r="B46" s="10"/>
       <c r="C46" s="10"/>
       <c r="D46" s="11">
@@ -1713,7 +1724,7 @@
       <c r="H46" s="34"/>
     </row>
     <row r="47" spans="1:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="A47" s="49">
+      <c r="A47" s="47">
         <v>15</v>
       </c>
       <c r="B47" s="15">
@@ -1735,7 +1746,7 @@
       </c>
     </row>
     <row r="48" spans="1:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="A48" s="49"/>
+      <c r="A48" s="47"/>
       <c r="B48" s="4">
         <f>B47+1</f>
         <v>30</v>
@@ -1755,7 +1766,7 @@
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A49" s="50"/>
+      <c r="A49" s="48"/>
       <c r="B49" s="10"/>
       <c r="C49" s="10"/>
       <c r="D49" s="11">
@@ -1768,7 +1779,7 @@
       <c r="H49" s="34"/>
     </row>
     <row r="50" spans="1:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="A50" s="49"/>
+      <c r="A50" s="47"/>
       <c r="B50" s="15"/>
       <c r="C50" s="4" t="s">
         <v>7</v>
@@ -1780,12 +1791,12 @@
       <c r="E50" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="H50" s="52" t="s">
+      <c r="H50" s="49" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="51" spans="1:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="A51" s="49"/>
+      <c r="A51" s="47"/>
       <c r="C51" s="4" t="s">
         <v>11</v>
       </c>
@@ -1796,10 +1807,10 @@
       <c r="E51" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="H51" s="53"/>
+      <c r="H51" s="50"/>
     </row>
     <row r="52" spans="1:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="A52" s="50"/>
+      <c r="A52" s="48"/>
       <c r="B52" s="10"/>
       <c r="C52" s="10"/>
       <c r="D52" s="11"/>
@@ -1812,14 +1823,6 @@
     </row>
   </sheetData>
   <mergeCells count="20">
-    <mergeCell ref="A50:A52"/>
-    <mergeCell ref="H50:H51"/>
-    <mergeCell ref="A32:A34"/>
-    <mergeCell ref="A35:A37"/>
-    <mergeCell ref="A38:A40"/>
-    <mergeCell ref="A41:A43"/>
-    <mergeCell ref="A44:A46"/>
-    <mergeCell ref="A47:A49"/>
     <mergeCell ref="F12:H12"/>
     <mergeCell ref="A14:A16"/>
     <mergeCell ref="A29:A31"/>
@@ -1832,6 +1835,14 @@
     <mergeCell ref="F22:H22"/>
     <mergeCell ref="A23:A25"/>
     <mergeCell ref="A26:A28"/>
+    <mergeCell ref="A50:A52"/>
+    <mergeCell ref="H50:H51"/>
+    <mergeCell ref="A32:A34"/>
+    <mergeCell ref="A35:A37"/>
+    <mergeCell ref="A38:A40"/>
+    <mergeCell ref="A41:A43"/>
+    <mergeCell ref="A44:A46"/>
+    <mergeCell ref="A47:A49"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup scale="78" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>

--- a/0-course-info/canvas/canvas_schedule.xlsx
+++ b/0-course-info/canvas/canvas_schedule.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/czmann/Documents/teaching/stat3540/0-course-info/canvas/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9B91504-18BC-DB4D-AA41-A543C9BC4D3C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66748238-5FDD-0B45-902D-516815C902C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17880" xr2:uid="{BA0A3FFF-9577-8249-B793-6919848B638A}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="75">
   <si>
     <t>Week</t>
   </si>
@@ -264,6 +264,21 @@
   </si>
   <si>
     <t>Lab 3 data collection due 10/9</t>
+  </si>
+  <si>
+    <t>Activity 7.1</t>
+  </si>
+  <si>
+    <t>Lecture Video: Residuals aren't Normal
+Lecture Video: Non-Constant Variance
+Lecture Video: Non-Parametric Tests</t>
+  </si>
+  <si>
+    <t>Lecture Video: Intro to Causal Inference
+Lecture Video: Causal Inference with Randomized Experiments</t>
+  </si>
+  <si>
+    <t>Activity 8.1</t>
   </si>
 </sst>
 </file>
@@ -373,7 +388,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="56">
+  <cellXfs count="57">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -539,6 +554,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1317,9 +1335,9 @@
         <v>38</v>
       </c>
       <c r="G21" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="H21" s="25" t="s">
+        <v>71</v>
+      </c>
+      <c r="H21" s="56" t="s">
         <v>70</v>
       </c>
     </row>
@@ -1334,7 +1352,7 @@
       <c r="G22" s="55"/>
       <c r="H22" s="55"/>
     </row>
-    <row r="23" spans="1:9" ht="20.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:9" ht="48" x14ac:dyDescent="0.2">
       <c r="A23" s="54">
         <v>8</v>
       </c>
@@ -1352,12 +1370,16 @@
       <c r="E23" s="17" t="s">
         <v>37</v>
       </c>
-      <c r="F23" s="18"/>
-      <c r="G23" s="18"/>
+      <c r="F23" s="18" t="s">
+        <v>72</v>
+      </c>
+      <c r="G23" s="18" t="s">
+        <v>39</v>
+      </c>
       <c r="H23" s="18"/>
       <c r="I23" s="8"/>
     </row>
-    <row r="24" spans="1:9" ht="20.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:9" ht="48" x14ac:dyDescent="0.2">
       <c r="A24" s="47"/>
       <c r="B24" s="4">
         <f>B23+1</f>
@@ -1372,6 +1394,12 @@
       </c>
       <c r="E24" s="6" t="s">
         <v>41</v>
+      </c>
+      <c r="F24" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="G24" s="9" t="s">
+        <v>74</v>
       </c>
       <c r="H24" s="26"/>
     </row>

--- a/0-course-info/canvas/canvas_schedule.xlsx
+++ b/0-course-info/canvas/canvas_schedule.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10909"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10927"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/czmann/Documents/teaching/stat3540/0-course-info/canvas/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66748238-5FDD-0B45-902D-516815C902C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57FF5F66-F96A-0241-909B-9E15CFDEDB77}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17880" xr2:uid="{BA0A3FFF-9577-8249-B793-6919848B638A}"/>
   </bookViews>
@@ -388,7 +388,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="57">
+  <cellXfs count="56">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -528,11 +528,20 @@
     <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -545,18 +554,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -930,7 +927,7 @@
       </c>
     </row>
     <row r="2" spans="1:8" ht="32" x14ac:dyDescent="0.2">
-      <c r="A2" s="47">
+      <c r="A2" s="49">
         <v>1</v>
       </c>
       <c r="B2" s="4">
@@ -953,7 +950,7 @@
       </c>
     </row>
     <row r="3" spans="1:8" ht="32" x14ac:dyDescent="0.2">
-      <c r="A3" s="47"/>
+      <c r="A3" s="49"/>
       <c r="B3" s="4">
         <v>2</v>
       </c>
@@ -975,7 +972,7 @@
       </c>
     </row>
     <row r="4" spans="1:8" ht="20.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="48"/>
+      <c r="A4" s="50"/>
       <c r="B4" s="10"/>
       <c r="C4" s="10"/>
       <c r="D4" s="11"/>
@@ -987,7 +984,7 @@
       </c>
     </row>
     <row r="5" spans="1:8" ht="48" x14ac:dyDescent="0.2">
-      <c r="A5" s="54">
+      <c r="A5" s="48">
         <v>2</v>
       </c>
       <c r="B5" s="15">
@@ -1013,7 +1010,7 @@
       <c r="H5" s="19"/>
     </row>
     <row r="6" spans="1:8" ht="48" x14ac:dyDescent="0.2">
-      <c r="A6" s="47"/>
+      <c r="A6" s="49"/>
       <c r="B6" s="4">
         <f>B5+1</f>
         <v>4</v>
@@ -1036,7 +1033,7 @@
       </c>
     </row>
     <row r="7" spans="1:8" ht="20.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="48"/>
+      <c r="A7" s="50"/>
       <c r="B7" s="10"/>
       <c r="C7" s="10"/>
       <c r="D7" s="11"/>
@@ -1046,7 +1043,7 @@
       <c r="H7" s="14"/>
     </row>
     <row r="8" spans="1:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="A8" s="47">
+      <c r="A8" s="49">
         <v>3</v>
       </c>
       <c r="B8" s="4">
@@ -1074,7 +1071,7 @@
       </c>
     </row>
     <row r="9" spans="1:8" ht="20.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="47"/>
+      <c r="A9" s="49"/>
       <c r="B9" s="4">
         <f>B8+1</f>
         <v>6</v>
@@ -1097,7 +1094,7 @@
       </c>
     </row>
     <row r="10" spans="1:8" ht="20.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="48"/>
+      <c r="A10" s="50"/>
       <c r="B10" s="10"/>
       <c r="C10" s="10"/>
       <c r="D10" s="11"/>
@@ -1109,7 +1106,7 @@
       </c>
     </row>
     <row r="11" spans="1:8" ht="32" x14ac:dyDescent="0.2">
-      <c r="A11" s="54">
+      <c r="A11" s="48">
         <v>4</v>
       </c>
       <c r="B11" s="15">
@@ -1134,7 +1131,7 @@
       </c>
     </row>
     <row r="12" spans="1:8" ht="20.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="47"/>
+      <c r="A12" s="49"/>
       <c r="B12" s="21">
         <f>B11+1</f>
         <v>8</v>
@@ -1149,14 +1146,14 @@
       <c r="E12" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="F12" s="53" t="s">
+      <c r="F12" s="47" t="s">
         <v>27</v>
       </c>
-      <c r="G12" s="53"/>
-      <c r="H12" s="53"/>
+      <c r="G12" s="47"/>
+      <c r="H12" s="47"/>
     </row>
     <row r="13" spans="1:8" ht="20.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="48"/>
+      <c r="A13" s="50"/>
       <c r="B13" s="10"/>
       <c r="C13" s="10"/>
       <c r="D13" s="11"/>
@@ -1168,7 +1165,7 @@
       </c>
     </row>
     <row r="14" spans="1:8" ht="20.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="54">
+      <c r="A14" s="48">
         <v>5</v>
       </c>
       <c r="B14" s="15">
@@ -1194,7 +1191,7 @@
       <c r="H14" s="19"/>
     </row>
     <row r="15" spans="1:8" ht="48" x14ac:dyDescent="0.2">
-      <c r="A15" s="47"/>
+      <c r="A15" s="49"/>
       <c r="B15" s="4">
         <f>B14+1</f>
         <v>10</v>
@@ -1218,7 +1215,7 @@
       <c r="H15" s="24"/>
     </row>
     <row r="16" spans="1:8" ht="20.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="48"/>
+      <c r="A16" s="50"/>
       <c r="B16" s="10"/>
       <c r="C16" s="10"/>
       <c r="D16" s="11"/>
@@ -1228,7 +1225,7 @@
       <c r="H16" s="14"/>
     </row>
     <row r="17" spans="1:9" ht="16" x14ac:dyDescent="0.2">
-      <c r="A17" s="54">
+      <c r="A17" s="48">
         <v>6</v>
       </c>
       <c r="B17" s="15">
@@ -1256,7 +1253,7 @@
       </c>
     </row>
     <row r="18" spans="1:9" ht="32" x14ac:dyDescent="0.2">
-      <c r="A18" s="47"/>
+      <c r="A18" s="49"/>
       <c r="B18" s="4">
         <f>B17+1</f>
         <v>12</v>
@@ -1278,8 +1275,8 @@
         <v>67</v>
       </c>
     </row>
-    <row r="19" spans="1:9" ht="20.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="48"/>
+    <row r="19" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A19" s="50"/>
       <c r="B19" s="10"/>
       <c r="C19" s="10"/>
       <c r="D19" s="11"/>
@@ -1290,7 +1287,7 @@
       </c>
     </row>
     <row r="20" spans="1:9" ht="20.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="54">
+      <c r="A20" s="48">
         <v>7</v>
       </c>
       <c r="B20" s="15">
@@ -1316,7 +1313,7 @@
       <c r="H20" s="18"/>
     </row>
     <row r="21" spans="1:9" ht="48" x14ac:dyDescent="0.2">
-      <c r="A21" s="47"/>
+      <c r="A21" s="49"/>
       <c r="B21" s="4">
         <f>B20+1</f>
         <v>14</v>
@@ -1337,23 +1334,23 @@
       <c r="G21" s="9" t="s">
         <v>71</v>
       </c>
-      <c r="H21" s="56" t="s">
+      <c r="H21" s="31" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="22" spans="1:9" ht="20.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="48"/>
+      <c r="A22" s="50"/>
       <c r="B22" s="10"/>
       <c r="C22" s="10"/>
       <c r="D22" s="11"/>
-      <c r="F22" s="55" t="s">
+      <c r="F22" s="51" t="s">
         <v>40</v>
       </c>
-      <c r="G22" s="55"/>
-      <c r="H22" s="55"/>
+      <c r="G22" s="51"/>
+      <c r="H22" s="51"/>
     </row>
     <row r="23" spans="1:9" ht="48" x14ac:dyDescent="0.2">
-      <c r="A23" s="54">
+      <c r="A23" s="48">
         <v>8</v>
       </c>
       <c r="B23" s="15">
@@ -1380,7 +1377,7 @@
       <c r="I23" s="8"/>
     </row>
     <row r="24" spans="1:9" ht="48" x14ac:dyDescent="0.2">
-      <c r="A24" s="47"/>
+      <c r="A24" s="49"/>
       <c r="B24" s="4">
         <f>B23+1</f>
         <v>16</v>
@@ -1404,7 +1401,7 @@
       <c r="H24" s="26"/>
     </row>
     <row r="25" spans="1:9" ht="20.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="48"/>
+      <c r="A25" s="50"/>
       <c r="B25" s="10"/>
       <c r="C25" s="10"/>
       <c r="D25" s="11"/>
@@ -1415,7 +1412,7 @@
       </c>
     </row>
     <row r="26" spans="1:9" ht="20.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="54">
+      <c r="A26" s="48">
         <v>9</v>
       </c>
       <c r="B26" s="27">
@@ -1437,7 +1434,7 @@
       <c r="H26" s="30"/>
     </row>
     <row r="27" spans="1:9" ht="20.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="47"/>
+      <c r="A27" s="49"/>
       <c r="B27" s="4">
         <f>B26+1</f>
         <v>18</v>
@@ -1458,7 +1455,7 @@
       <c r="H27" s="31"/>
     </row>
     <row r="28" spans="1:9" ht="20.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="48"/>
+      <c r="A28" s="50"/>
       <c r="B28" s="10"/>
       <c r="C28" s="10"/>
       <c r="D28" s="11"/>
@@ -1468,7 +1465,7 @@
       <c r="H28" s="14"/>
     </row>
     <row r="29" spans="1:9" ht="20.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="47">
+      <c r="A29" s="49">
         <v>10</v>
       </c>
       <c r="B29" s="15">
@@ -1488,7 +1485,7 @@
       <c r="H29" s="9"/>
     </row>
     <row r="30" spans="1:9" ht="20.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="47"/>
+      <c r="A30" s="49"/>
       <c r="B30" s="4">
         <f>B29+1</f>
         <v>20</v>
@@ -1505,7 +1502,7 @@
       </c>
     </row>
     <row r="31" spans="1:9" ht="20.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="48"/>
+      <c r="A31" s="50"/>
       <c r="B31" s="10"/>
       <c r="C31" s="10"/>
       <c r="D31" s="11"/>
@@ -1515,7 +1512,7 @@
       <c r="H31" s="34"/>
     </row>
     <row r="32" spans="1:9" ht="16" x14ac:dyDescent="0.2">
-      <c r="A32" s="47">
+      <c r="A32" s="49">
         <v>11</v>
       </c>
       <c r="B32" s="15">
@@ -1537,7 +1534,7 @@
       </c>
     </row>
     <row r="33" spans="1:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="A33" s="47"/>
+      <c r="A33" s="49"/>
       <c r="B33" s="4">
         <f>B32+1</f>
         <v>22</v>
@@ -1554,7 +1551,7 @@
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A34" s="48"/>
+      <c r="A34" s="50"/>
       <c r="B34" s="10"/>
       <c r="C34" s="10"/>
       <c r="D34" s="11"/>
@@ -1564,7 +1561,7 @@
       <c r="H34" s="34"/>
     </row>
     <row r="35" spans="1:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="A35" s="47">
+      <c r="A35" s="49">
         <v>12</v>
       </c>
       <c r="B35" s="15">
@@ -1584,7 +1581,7 @@
       <c r="H35" s="9"/>
     </row>
     <row r="36" spans="1:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="A36" s="47"/>
+      <c r="A36" s="49"/>
       <c r="B36" s="4">
         <f>B35+1</f>
         <v>24</v>
@@ -1601,7 +1598,7 @@
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A37" s="48"/>
+      <c r="A37" s="50"/>
       <c r="B37" s="10"/>
       <c r="C37" s="10"/>
       <c r="D37" s="11"/>
@@ -1611,7 +1608,7 @@
       <c r="H37" s="34"/>
     </row>
     <row r="38" spans="1:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="A38" s="47">
+      <c r="A38" s="49">
         <v>13</v>
       </c>
       <c r="B38" s="15">
@@ -1631,7 +1628,7 @@
       <c r="H38" s="9"/>
     </row>
     <row r="39" spans="1:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="A39" s="47"/>
+      <c r="A39" s="49"/>
       <c r="B39" s="4">
         <f>B38+1</f>
         <v>26</v>
@@ -1648,7 +1645,7 @@
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A40" s="48"/>
+      <c r="A40" s="50"/>
       <c r="B40" s="10"/>
       <c r="C40" s="10"/>
       <c r="D40" s="11"/>
@@ -1660,7 +1657,7 @@
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A41" s="51"/>
+      <c r="A41" s="54"/>
       <c r="B41" s="36"/>
       <c r="C41" s="35" t="s">
         <v>7</v>
@@ -1675,7 +1672,7 @@
       <c r="H41" s="39"/>
     </row>
     <row r="42" spans="1:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="A42" s="51"/>
+      <c r="A42" s="54"/>
       <c r="B42" s="35"/>
       <c r="C42" s="35" t="s">
         <v>11</v>
@@ -1692,7 +1689,7 @@
       <c r="H42" s="41"/>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A43" s="52"/>
+      <c r="A43" s="55"/>
       <c r="B43" s="42"/>
       <c r="C43" s="42"/>
       <c r="D43" s="43"/>
@@ -1702,7 +1699,7 @@
       <c r="H43" s="46"/>
     </row>
     <row r="44" spans="1:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="A44" s="47">
+      <c r="A44" s="49">
         <v>14</v>
       </c>
       <c r="B44" s="15">
@@ -1722,7 +1719,7 @@
       <c r="H44" s="9"/>
     </row>
     <row r="45" spans="1:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="A45" s="47"/>
+      <c r="A45" s="49"/>
       <c r="B45" s="4">
         <f>B44+1</f>
         <v>28</v>
@@ -1739,7 +1736,7 @@
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A46" s="48"/>
+      <c r="A46" s="50"/>
       <c r="B46" s="10"/>
       <c r="C46" s="10"/>
       <c r="D46" s="11">
@@ -1752,7 +1749,7 @@
       <c r="H46" s="34"/>
     </row>
     <row r="47" spans="1:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="A47" s="47">
+      <c r="A47" s="49">
         <v>15</v>
       </c>
       <c r="B47" s="15">
@@ -1774,7 +1771,7 @@
       </c>
     </row>
     <row r="48" spans="1:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="A48" s="47"/>
+      <c r="A48" s="49"/>
       <c r="B48" s="4">
         <f>B47+1</f>
         <v>30</v>
@@ -1794,7 +1791,7 @@
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A49" s="48"/>
+      <c r="A49" s="50"/>
       <c r="B49" s="10"/>
       <c r="C49" s="10"/>
       <c r="D49" s="11">
@@ -1807,7 +1804,7 @@
       <c r="H49" s="34"/>
     </row>
     <row r="50" spans="1:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="A50" s="47"/>
+      <c r="A50" s="49"/>
       <c r="B50" s="15"/>
       <c r="C50" s="4" t="s">
         <v>7</v>
@@ -1819,12 +1816,12 @@
       <c r="E50" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="H50" s="49" t="s">
+      <c r="H50" s="52" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="51" spans="1:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="A51" s="47"/>
+      <c r="A51" s="49"/>
       <c r="C51" s="4" t="s">
         <v>11</v>
       </c>
@@ -1835,10 +1832,10 @@
       <c r="E51" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="H51" s="50"/>
+      <c r="H51" s="53"/>
     </row>
     <row r="52" spans="1:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="A52" s="48"/>
+      <c r="A52" s="50"/>
       <c r="B52" s="10"/>
       <c r="C52" s="10"/>
       <c r="D52" s="11"/>
@@ -1851,6 +1848,14 @@
     </row>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="A50:A52"/>
+    <mergeCell ref="H50:H51"/>
+    <mergeCell ref="A32:A34"/>
+    <mergeCell ref="A35:A37"/>
+    <mergeCell ref="A38:A40"/>
+    <mergeCell ref="A41:A43"/>
+    <mergeCell ref="A44:A46"/>
+    <mergeCell ref="A47:A49"/>
     <mergeCell ref="F12:H12"/>
     <mergeCell ref="A14:A16"/>
     <mergeCell ref="A29:A31"/>
@@ -1863,14 +1868,6 @@
     <mergeCell ref="F22:H22"/>
     <mergeCell ref="A23:A25"/>
     <mergeCell ref="A26:A28"/>
-    <mergeCell ref="A50:A52"/>
-    <mergeCell ref="H50:H51"/>
-    <mergeCell ref="A32:A34"/>
-    <mergeCell ref="A35:A37"/>
-    <mergeCell ref="A38:A40"/>
-    <mergeCell ref="A41:A43"/>
-    <mergeCell ref="A44:A46"/>
-    <mergeCell ref="A47:A49"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup scale="78" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>

--- a/0-course-info/canvas/canvas_schedule.xlsx
+++ b/0-course-info/canvas/canvas_schedule.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10927"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11011"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/czmann/Documents/teaching/stat3540/0-course-info/canvas/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57FF5F66-F96A-0241-909B-9E15CFDEDB77}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C61060CD-0182-CC4B-AFB4-E4EE2F9CD8B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17880" xr2:uid="{BA0A3FFF-9577-8249-B793-6919848B638A}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="89">
   <si>
     <t>Week</t>
   </si>
@@ -187,21 +187,6 @@
     <t>Mod 9: Observational Studies</t>
   </si>
   <si>
-    <t>Activity 9.1 + Start Lab 4</t>
-  </si>
-  <si>
-    <t>Mod 10: Writing Survey Instruments</t>
-  </si>
-  <si>
-    <t>Project Proposal due Wed 11/4</t>
-  </si>
-  <si>
-    <t>Mod 11: Survey Sampling</t>
-  </si>
-  <si>
-    <t>Mod 12: Survey Weights</t>
-  </si>
-  <si>
     <t>THANKSGIVING BREAK</t>
   </si>
   <si>
@@ -279,6 +264,71 @@
   </si>
   <si>
     <t>Activity 8.1</t>
+  </si>
+  <si>
+    <t>Activity 9.1</t>
+  </si>
+  <si>
+    <t>No prep!</t>
+  </si>
+  <si>
+    <t>Mod 10: Survey Sampling</t>
+  </si>
+  <si>
+    <t>Lecture Video: Survey Sampling Termonology
+Lecture Video: Types of Sampling
+Lecture Video: Simple Random Sample</t>
+  </si>
+  <si>
+    <t>Lecture Video: Types of Errors
+Lecture Video: Stratified Random Sampling</t>
+  </si>
+  <si>
+    <t>Lecture Video: Estimation with Simple Random Sampling
+Lecture Video: Estimation with Stratified Random Sampling</t>
+  </si>
+  <si>
+    <t>Lecture Video: Systematic Sampling
+Lecture Video: Estimation with Survey Weights</t>
+  </si>
+  <si>
+    <t>Final Project Proposal due Wed 11/4</t>
+  </si>
+  <si>
+    <t>Activity 9.2</t>
+  </si>
+  <si>
+    <t>Introduce Lab 4
+Activity 10.1</t>
+  </si>
+  <si>
+    <t>Activity 10.2</t>
+  </si>
+  <si>
+    <t>Activity 10.3</t>
+  </si>
+  <si>
+    <t>Mod 11: Survey Weights</t>
+  </si>
+  <si>
+    <t>Mod 12: Writing Survey Instruments</t>
+  </si>
+  <si>
+    <t>Activity 11.1</t>
+  </si>
+  <si>
+    <t>Activity 12 continued</t>
+  </si>
+  <si>
+    <t>Activity 12</t>
+  </si>
+  <si>
+    <t>Lab 4 checkpoint due Wed 11/11</t>
+  </si>
+  <si>
+    <t>Lecture Video: Covariate Adjustment
+Lecture Video: Types of Observational Studies
+Lecture Video: Administrative Data</t>
   </si>
 </sst>
 </file>
@@ -965,7 +1015,7 @@
         <v>8</v>
       </c>
       <c r="F3" s="9" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="G3" s="9" t="s">
         <v>12</v>
@@ -980,7 +1030,7 @@
       <c r="F4" s="13"/>
       <c r="G4" s="13"/>
       <c r="H4" s="14" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="48" x14ac:dyDescent="0.2">
@@ -1067,7 +1117,7 @@
         <v>20</v>
       </c>
       <c r="H8" s="8" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="20.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -1102,7 +1152,7 @@
       <c r="F10" s="13"/>
       <c r="G10" s="13"/>
       <c r="H10" s="14" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="32" x14ac:dyDescent="0.2">
@@ -1161,7 +1211,7 @@
       <c r="F13" s="13"/>
       <c r="G13" s="13"/>
       <c r="H13" s="31" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="20.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -1186,7 +1236,7 @@
         <v>28</v>
       </c>
       <c r="G14" s="9" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="H14" s="19"/>
     </row>
@@ -1246,10 +1296,10 @@
         <v>32</v>
       </c>
       <c r="G17" s="9" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="H17" s="9" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
     </row>
     <row r="18" spans="1:9" ht="32" x14ac:dyDescent="0.2">
@@ -1272,7 +1322,7 @@
         <v>34</v>
       </c>
       <c r="G18" s="9" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
     </row>
     <row r="19" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.2">
@@ -1283,7 +1333,7 @@
       <c r="F19" s="13"/>
       <c r="G19" s="13"/>
       <c r="H19" s="25" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
     </row>
     <row r="20" spans="1:9" ht="20.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -1332,10 +1382,10 @@
         <v>38</v>
       </c>
       <c r="G21" s="9" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="H21" s="31" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
     </row>
     <row r="22" spans="1:9" ht="20.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -1368,7 +1418,7 @@
         <v>37</v>
       </c>
       <c r="F23" s="18" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="G23" s="18" t="s">
         <v>39</v>
@@ -1393,10 +1443,10 @@
         <v>41</v>
       </c>
       <c r="F24" s="9" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="G24" s="9" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="H24" s="26"/>
     </row>
@@ -1449,8 +1499,11 @@
       <c r="E27" s="6" t="s">
         <v>44</v>
       </c>
+      <c r="F27" s="9" t="s">
+        <v>71</v>
+      </c>
       <c r="G27" s="9" t="s">
-        <v>45</v>
+        <v>70</v>
       </c>
       <c r="H27" s="31"/>
     </row>
@@ -1464,7 +1517,7 @@
       <c r="G28" s="13"/>
       <c r="H28" s="14"/>
     </row>
-    <row r="29" spans="1:9" ht="20.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:9" ht="48" x14ac:dyDescent="0.2">
       <c r="A29" s="49">
         <v>10</v>
       </c>
@@ -1482,9 +1535,15 @@
       <c r="E29" s="6" t="s">
         <v>44</v>
       </c>
+      <c r="F29" s="9" t="s">
+        <v>88</v>
+      </c>
+      <c r="G29" s="9" t="s">
+        <v>78</v>
+      </c>
       <c r="H29" s="9"/>
     </row>
-    <row r="30" spans="1:9" ht="20.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:9" ht="48" x14ac:dyDescent="0.2">
       <c r="A30" s="49"/>
       <c r="B30" s="4">
         <f>B29+1</f>
@@ -1498,7 +1557,13 @@
         <v>46324</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>46</v>
+        <v>72</v>
+      </c>
+      <c r="F30" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="G30" s="9" t="s">
+        <v>79</v>
       </c>
     </row>
     <row r="31" spans="1:9" ht="20.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -1511,7 +1576,7 @@
       <c r="G31" s="33"/>
       <c r="H31" s="34"/>
     </row>
-    <row r="32" spans="1:9" ht="16" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:9" ht="32" x14ac:dyDescent="0.2">
       <c r="A32" s="49">
         <v>11</v>
       </c>
@@ -1527,13 +1592,19 @@
         <v>46329</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>46</v>
+        <v>72</v>
+      </c>
+      <c r="F32" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="G32" s="9" t="s">
+        <v>80</v>
       </c>
       <c r="H32" s="9" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="33" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" ht="64" x14ac:dyDescent="0.2">
       <c r="A33" s="49"/>
       <c r="B33" s="4">
         <f>B32+1</f>
@@ -1547,7 +1618,13 @@
         <v>46331</v>
       </c>
       <c r="E33" s="6" t="s">
-        <v>46</v>
+        <v>72</v>
+      </c>
+      <c r="F33" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="G33" s="9" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.2">
@@ -1560,7 +1637,7 @@
       <c r="G34" s="33"/>
       <c r="H34" s="34"/>
     </row>
-    <row r="35" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:8" ht="44" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="49">
         <v>12</v>
       </c>
@@ -1576,9 +1653,17 @@
         <v>46336</v>
       </c>
       <c r="E35" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="H35" s="9"/>
+        <v>82</v>
+      </c>
+      <c r="F35" s="9" t="s">
+        <v>76</v>
+      </c>
+      <c r="G35" s="9" t="s">
+        <v>84</v>
+      </c>
+      <c r="H35" s="8" t="s">
+        <v>87</v>
+      </c>
     </row>
     <row r="36" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A36" s="49"/>
@@ -1594,7 +1679,10 @@
         <v>46338</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>48</v>
+        <v>83</v>
+      </c>
+      <c r="G36" s="9" t="s">
+        <v>86</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.2">
@@ -1623,7 +1711,10 @@
         <v>46343</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>48</v>
+        <v>83</v>
+      </c>
+      <c r="G38" s="9" t="s">
+        <v>85</v>
       </c>
       <c r="H38" s="9"/>
     </row>
@@ -1641,7 +1732,10 @@
         <v>46345</v>
       </c>
       <c r="E39" s="6" t="s">
-        <v>49</v>
+        <v>83</v>
+      </c>
+      <c r="G39" s="9" t="s">
+        <v>85</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.2">
@@ -1653,7 +1747,7 @@
       <c r="F40" s="33"/>
       <c r="G40" s="33"/>
       <c r="H40" s="25" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.2">
@@ -1682,7 +1776,7 @@
         <v>46352</v>
       </c>
       <c r="E42" s="38" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="F42" s="39"/>
       <c r="G42" s="39"/>
@@ -1714,7 +1808,7 @@
         <v>46357</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="H44" s="9"/>
     </row>
@@ -1732,7 +1826,7 @@
         <v>46359</v>
       </c>
       <c r="E45" s="6" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.2">
@@ -1764,10 +1858,10 @@
         <v>46364</v>
       </c>
       <c r="E47" s="6" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="H47" s="8" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
     </row>
     <row r="48" spans="1:8" ht="16" x14ac:dyDescent="0.2">
@@ -1784,10 +1878,10 @@
         <v>46366</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="H48" s="8" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.2">
@@ -1814,10 +1908,10 @@
         <v>46371</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="H50" s="52" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
     </row>
     <row r="51" spans="1:8" ht="16" x14ac:dyDescent="0.2">
@@ -1830,7 +1924,7 @@
         <v>46373</v>
       </c>
       <c r="E51" s="6" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="H51" s="53"/>
     </row>
@@ -1840,7 +1934,7 @@
       <c r="C52" s="10"/>
       <c r="D52" s="11"/>
       <c r="E52" s="12" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="F52" s="33"/>
       <c r="G52" s="33"/>

--- a/0-course-info/canvas/canvas_schedule.xlsx
+++ b/0-course-info/canvas/canvas_schedule.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/czmann/Documents/teaching/stat3540/0-course-info/canvas/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C61060CD-0182-CC4B-AFB4-E4EE2F9CD8B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59845E7C-1546-4C46-AE4D-1F0E96A80900}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17880" xr2:uid="{BA0A3FFF-9577-8249-B793-6919848B638A}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="90">
   <si>
     <t>Week</t>
   </si>
@@ -292,9 +292,6 @@
 Lecture Video: Estimation with Survey Weights</t>
   </si>
   <si>
-    <t>Final Project Proposal due Wed 11/4</t>
-  </si>
-  <si>
     <t>Activity 9.2</t>
   </si>
   <si>
@@ -326,9 +323,14 @@
     <t>Lab 4 checkpoint due Wed 11/11</t>
   </si>
   <si>
-    <t>Lecture Video: Covariate Adjustment
-Lecture Video: Types of Observational Studies
+    <t>Lecture Video: Types of Observational Studies
 Lecture Video: Administrative Data</t>
+  </si>
+  <si>
+    <t>Final Project Proposal due Fri 11/13</t>
+  </si>
+  <si>
+    <t>Lab 4 checkpoint due Wed 11/4</t>
   </si>
 </sst>
 </file>
@@ -1517,7 +1519,7 @@
       <c r="G28" s="13"/>
       <c r="H28" s="14"/>
     </row>
-    <row r="29" spans="1:9" ht="48" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:9" ht="32" x14ac:dyDescent="0.2">
       <c r="A29" s="49">
         <v>10</v>
       </c>
@@ -1536,10 +1538,10 @@
         <v>44</v>
       </c>
       <c r="F29" s="9" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G29" s="9" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H29" s="9"/>
     </row>
@@ -1563,7 +1565,7 @@
         <v>73</v>
       </c>
       <c r="G30" s="9" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="31" spans="1:9" ht="20.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -1574,7 +1576,7 @@
       <c r="E31" s="32"/>
       <c r="F31" s="33"/>
       <c r="G31" s="33"/>
-      <c r="H31" s="34"/>
+      <c r="H31" s="14"/>
     </row>
     <row r="32" spans="1:9" ht="32" x14ac:dyDescent="0.2">
       <c r="A32" s="49">
@@ -1598,10 +1600,10 @@
         <v>74</v>
       </c>
       <c r="G32" s="9" t="s">
-        <v>80</v>
-      </c>
-      <c r="H32" s="9" t="s">
-        <v>77</v>
+        <v>79</v>
+      </c>
+      <c r="H32" s="8" t="s">
+        <v>89</v>
       </c>
     </row>
     <row r="33" spans="1:8" ht="64" x14ac:dyDescent="0.2">
@@ -1624,8 +1626,9 @@
         <v>75</v>
       </c>
       <c r="G33" s="9" t="s">
-        <v>81</v>
-      </c>
+        <v>80</v>
+      </c>
+      <c r="H33" s="9"/>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A34" s="50"/>
@@ -1653,16 +1656,16 @@
         <v>46336</v>
       </c>
       <c r="E35" s="6" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F35" s="9" t="s">
         <v>76</v>
       </c>
       <c r="G35" s="9" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="H35" s="8" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="36" spans="1:8" ht="16" x14ac:dyDescent="0.2">
@@ -1679,10 +1682,13 @@
         <v>46338</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="G36" s="9" t="s">
-        <v>86</v>
+        <v>85</v>
+      </c>
+      <c r="H36" s="8" t="s">
+        <v>88</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.2">
@@ -1711,10 +1717,10 @@
         <v>46343</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="G38" s="9" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H38" s="9"/>
     </row>
@@ -1732,10 +1738,10 @@
         <v>46345</v>
       </c>
       <c r="E39" s="6" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="G39" s="9" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.2">
